--- a/ebegu-server/src/main/resources/reporting/Zahlungen_DE.xlsx
+++ b/ebegu-server/src/main/resources/reporting/Zahlungen_DE.xlsx
@@ -1,29 +1,29 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26626"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27830"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\projects\ebegu-server\src\main\resources\reporting\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\java\kibon\ebegu-server\src\main\resources\reporting\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ACA96275-A45E-4162-8265-C83A83CC6E75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7129528D-351C-44E0-AF8F-3C98A3B6A5F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="17640" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15840" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="1" r:id="rId1"/>
-    <sheet name="Auszahlungen an Institution" sheetId="2" r:id="rId2"/>
-    <sheet name="Zahlungen ausserhalb kiBon" sheetId="3" r:id="rId3"/>
+    <sheet name="Auszahlung nach Kind" sheetId="2" r:id="rId2"/>
+    <sheet name="Auszahlung nach Gemeinde" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Data!$A$10:$N$10</definedName>
-    <definedName name="data">Data!$A$10:$P$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Data!$A$10:$P$10</definedName>
+    <definedName name="data">Data!$A$10:$R$11</definedName>
   </definedNames>
   <calcPr calcId="191029" iterateDelta="1E-4"/>
   <pivotCaches>
-    <pivotCache cacheId="1" r:id="rId4"/>
+    <pivotCache cacheId="0" r:id="rId4"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="62">
   <si>
     <t>Zahlungen</t>
   </si>
@@ -122,9 +122,6 @@
     <t>Nicht leer</t>
   </si>
   <si>
-    <t>Auszahlung an</t>
-  </si>
-  <si>
     <t>{zahlungslaufTitle}</t>
   </si>
   <si>
@@ -176,36 +173,136 @@
     <t>{repeatRow}</t>
   </si>
   <si>
-    <t>Auszahlungen an Institution</t>
-  </si>
-  <si>
-    <t>- all -</t>
-  </si>
-  <si>
     <t>Summe von Betrag in CHF</t>
   </si>
   <si>
     <t>x</t>
   </si>
   <si>
-    <t>Total Result</t>
-  </si>
-  <si>
-    <t>Zahlungen, die durch die Gemeinde ausserhalb von kiBon an die Antragstellenden gemacht werden müssen</t>
-  </si>
-  <si>
-    <t>Zahlungen ausserhalb kiBon</t>
+    <t>Nachname, Vorname</t>
+  </si>
+  <si>
+    <t>(Mehrere Elemente)</t>
+  </si>
+  <si>
+    <t>{kindNachname} {kindVorname}</t>
+  </si>
+  <si>
+    <t>Spaltenbeschriftungen</t>
+  </si>
+  <si>
+    <t>Verfügte Betreuungsgutscheine</t>
+  </si>
+  <si>
+    <t>Filter</t>
+  </si>
+  <si>
+    <t>Monat</t>
+  </si>
+  <si>
+    <t>Übersicht Auszahlungen: nach Gemeinde</t>
+  </si>
+  <si>
+    <t>Übersicht Auszahlungen: nach Kind</t>
+  </si>
+  <si>
+    <t>Auszahlung an Institution</t>
+  </si>
+  <si>
+    <t>Auszahlung an (für Gemeinde Pivot)</t>
+  </si>
+  <si>
+    <t>Auszahlung an (für Kind Pivot)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Verfügte Betreuungsgutscheine: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Höhe des Betreuungsgutscheins pro Kind und Monat gemäss der aktuell gültigen Verfügung. Der Betrag beinhaltet Korrekturen, welche in den Zahlungslauf mit der Institution übernommen wurden, so wie auch Zahlungen, die nicht in den Zahlungslauf mit der Institution übernommen wurden und direkt zwischen Gemeinde und Erziehungsberechtigten abgerechnet werden.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Auszahlung an Institution:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Betrag, der von der Gemeinde an die Institution überwiesen wurde. Der Betrag beinhaltet Korrekturen, welche in den Zahlungslauf mit der Institution übernommen wurden. Dieser Betrag wird in der Rechnung an die Erziehungsberechtigten von den Vollkosten abgezogen.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Abrechnung direkt zwischen Gemeinde &amp; Erziehungsberechtigten:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Korrekturbetrag zum effektiven Gutschein. Entspricht dem Differenzbetrag von dem an die Institution ausbezahlten Betrag und dem aktuell gültigen Betreuungsgutschein. Dieser Korrekturbetrag wird ausserhalb von kiBon von der Gemeinde direkt mit den Erziehungsberechtigten beglichen.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Auszahlung an Institution:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Betrag, der von der Gemeinde an die Institution überwiesen wurde. Wird in der Rechnung an die Erziehungsberechtigten von den Vollkosten abgezogen.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Ausserhalb von kiBon: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Korrekturbetrag, welcher ausserhalb von kiBon von der Gemeinde direkt mit den Erziehungsberechtigten beglichen wird. Differenzbetrag von dem an die Institution ausbezahlten Betrag und dem aktuell gültigen Betreuungsgutschein.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Verfügte Betreuungsgutscheine: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Höhe des Betreuungsgutscheins pro Kind und Monat gemäss der aktuell gültigen Verfügung.</t>
+    </r>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
-    <numFmt numFmtId="165" formatCode="m/d/yyyy\ h:mm"/>
-    <numFmt numFmtId="166" formatCode="&quot;CHF &quot;#,##0.00"/>
+  <numFmts count="3">
+    <numFmt numFmtId="164" formatCode="m/d/yyyy\ h:mm"/>
+    <numFmt numFmtId="165" formatCode="&quot;CHF &quot;#,##0.00"/>
+    <numFmt numFmtId="166" formatCode="mmm"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -237,19 +334,34 @@
       <charset val="1"/>
     </font>
     <font>
-      <b/>
-      <sz val="12"/>
+      <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="1"/>
     </font>
     <font>
+      <b/>
+      <sz val="16"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="5">
@@ -278,7 +390,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="28">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -301,353 +413,27 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right/>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyBorder="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyBorder="0" applyProtection="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyBorder="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyBorder="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyBorder="0" applyProtection="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="58">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -656,13 +442,13 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="10" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -672,70 +458,12 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="4"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="3" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="3" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="3" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="4" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="3" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="4" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="4" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="2" applyBorder="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="6" applyBorder="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="2" applyBorder="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="2" applyBorder="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="2" applyBorder="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="7" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="5" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="2" applyBorder="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="2" applyBorder="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="7" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="5" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="2" applyBorder="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="2" applyBorder="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="7" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="5" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="6" applyBorder="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="6" applyBorder="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="6" applyBorder="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="5" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="5" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="26" xfId="4" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="27" xfId="3" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="7" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="7" applyBorder="1"/>
     <xf numFmtId="14" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="14" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
@@ -744,6 +472,38 @@
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="9">
     <cellStyle name="Neutral 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000006000000}"/>
@@ -756,11 +516,73 @@
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
     <cellStyle name="Standard 2" xfId="8" xr:uid="{00000000-0005-0000-0000-00000D000000}"/>
   </cellStyles>
-  <dxfs count="1">
+  <dxfs count="21">
     <dxf>
       <font>
         <color rgb="FFFF0000"/>
       </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1" indent="0"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1" indent="0"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1" indent="0"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1" indent="0"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1" indent="0"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1" indent="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="mmm"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -844,22 +666,16 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedDate="0" createdVersion="3" recordCount="1" xr:uid="{00000000-000A-0000-FFFF-FFFF01000000}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Brunner Anita" refreshedDate="45519.518409027776" createdVersion="3" refreshedVersion="8" recordCount="2" xr:uid="{00000000-000A-0000-FFFF-FFFF01000000}">
   <cacheSource type="worksheet">
-    <worksheetSource ref="A10:R1048576" sheet="Data"/>
+    <worksheetSource ref="A10:U1048576" sheet="Data"/>
   </cacheSource>
-  <cacheFields count="18">
+  <cacheFields count="21">
     <cacheField name="Titel Zahlungslauf" numFmtId="0">
-      <sharedItems containsBlank="1" count="2">
-        <s v="{zahlungslaufTitle}"/>
-        <m/>
-      </sharedItems>
-    </cacheField>
-    <cacheField name="Fälligkeitsdatum" numFmtId="0">
-      <sharedItems containsBlank="1" count="2">
-        <s v="{faelligkeitsDatum}"/>
-        <m/>
-      </sharedItems>
+      <sharedItems containsBlank="1"/>
+    </cacheField>
+    <cacheField name="Fälligkeitsdatum" numFmtId="14">
+      <sharedItems containsBlank="1"/>
     </cacheField>
     <cacheField name="Gemeinde" numFmtId="0">
       <sharedItems containsBlank="1" count="2">
@@ -873,21 +689,18 @@
         <m/>
       </sharedItems>
     </cacheField>
-    <cacheField name="Erstellungsdatum Zahlungslauf" numFmtId="0">
+    <cacheField name="Erstellungsdatum Zahlungslauf" numFmtId="164">
+      <sharedItems containsBlank="1"/>
+    </cacheField>
+    <cacheField name="Kind Nachname" numFmtId="0">
+      <sharedItems containsBlank="1"/>
+    </cacheField>
+    <cacheField name="Kind Vorname" numFmtId="0">
+      <sharedItems containsBlank="1"/>
+    </cacheField>
+    <cacheField name="Nachname, Vorname" numFmtId="0">
       <sharedItems containsBlank="1" count="2">
-        <s v="{timestampZahlungslauf}"/>
-        <m/>
-      </sharedItems>
-    </cacheField>
-    <cacheField name="Kind Nachname" numFmtId="0">
-      <sharedItems containsBlank="1" count="2">
-        <s v="{kindNachname}"/>
-        <m/>
-      </sharedItems>
-    </cacheField>
-    <cacheField name="Kind Vorname" numFmtId="0">
-      <sharedItems containsBlank="1" count="2">
-        <s v="{kindVorname}"/>
+        <s v="{kindNachname} {kindVorname}"/>
         <m/>
       </sharedItems>
     </cacheField>
@@ -897,63 +710,56 @@
         <m/>
       </sharedItems>
     </cacheField>
-    <cacheField name="von" numFmtId="0">
+    <cacheField name="von" numFmtId="14">
       <sharedItems containsBlank="1" count="2">
         <s v="{zeitabschnittVon}"/>
         <m/>
       </sharedItems>
     </cacheField>
-    <cacheField name="bis" numFmtId="0">
+    <cacheField name="Monat" numFmtId="0">
       <sharedItems containsBlank="1" count="2">
-        <s v="{zeitabschnittBis}"/>
+        <s v="{zeitabschnittVon}"/>
         <m/>
       </sharedItems>
     </cacheField>
-    <cacheField name="BG-Pensum" numFmtId="0">
-      <sharedItems containsBlank="1" count="2">
-        <s v="{bgPensum}"/>
-        <m/>
-      </sharedItems>
-    </cacheField>
-    <cacheField name="Betrag in CHF" numFmtId="0">
-      <sharedItems containsBlank="1" count="2">
-        <s v="{betrag}"/>
-        <m/>
-      </sharedItems>
+    <cacheField name="bis" numFmtId="14">
+      <sharedItems containsBlank="1"/>
+    </cacheField>
+    <cacheField name="BG-Pensum" numFmtId="10">
+      <sharedItems containsBlank="1"/>
+    </cacheField>
+    <cacheField name="Betrag in CHF" numFmtId="165">
+      <sharedItems containsBlank="1"/>
     </cacheField>
     <cacheField name="Korrektur" numFmtId="0">
-      <sharedItems containsBlank="1" count="2">
-        <s v="{korrektur}"/>
-        <m/>
-      </sharedItems>
+      <sharedItems containsBlank="1"/>
     </cacheField>
     <cacheField name="In Zahlungslauf ignorieren" numFmtId="0">
-      <sharedItems containsBlank="1" count="2">
-        <s v="{ignorieren}"/>
-        <m/>
-      </sharedItems>
+      <sharedItems containsBlank="1"/>
     </cacheField>
     <cacheField name="IBAN Eltern" numFmtId="0">
-      <sharedItems containsBlank="1" count="2">
-        <s v="{ibanEltern}"/>
-        <m/>
-      </sharedItems>
+      <sharedItems containsBlank="1"/>
     </cacheField>
     <cacheField name="Kontoname Eltern" numFmtId="0">
-      <sharedItems containsBlank="1" count="2">
-        <s v="{kontoEltern}"/>
-        <m/>
-      </sharedItems>
+      <sharedItems containsBlank="1"/>
     </cacheField>
     <cacheField name="Nicht leer" numFmtId="0">
-      <sharedItems containsBlank="1" count="2">
+      <sharedItems containsBlank="1" count="3">
         <s v="x"/>
         <m/>
+        <s v="" u="1"/>
       </sharedItems>
     </cacheField>
-    <cacheField name="Auszahlung an" numFmtId="0">
+    <cacheField name="Auszahlung an (für Kind Pivot)" numFmtId="0">
+      <sharedItems containsBlank="1" count="3">
+        <s v="Auszahlung an Institution"/>
+        <m/>
+        <e v="#REF!" u="1"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Auszahlung an (für Gemeinde Pivot)" numFmtId="0">
       <sharedItems containsBlank="1" count="2">
-        <s v="Ausserhalb kiBon"/>
+        <s v="Auszahlung an Institution"/>
         <m/>
       </sharedItems>
     </cacheField>
@@ -967,97 +773,239 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheRecords1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" count="1">
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="2">
   <r>
+    <s v="{zahlungslaufTitle}"/>
+    <s v="{faelligkeitsDatum}"/>
+    <x v="0"/>
+    <x v="0"/>
+    <s v="{timestampZahlungslauf}"/>
+    <s v="{kindNachname}"/>
+    <s v="{kindVorname}"/>
     <x v="0"/>
     <x v="0"/>
     <x v="0"/>
     <x v="0"/>
+    <s v="{zeitabschnittBis}"/>
+    <s v="{bgPensum}"/>
+    <s v="{betrag}"/>
+    <s v="{korrektur}"/>
+    <s v="{ignorieren}"/>
+    <s v="{ibanEltern}"/>
+    <s v="{kontoEltern}"/>
     <x v="0"/>
     <x v="0"/>
     <x v="0"/>
-    <x v="0"/>
-    <x v="0"/>
-    <x v="0"/>
-    <x v="0"/>
-    <x v="0"/>
-    <x v="0"/>
-    <x v="0"/>
-    <x v="0"/>
-    <x v="0"/>
-    <x v="0"/>
-    <x v="0"/>
+  </r>
+  <r>
+    <m/>
+    <m/>
+    <x v="1"/>
+    <x v="1"/>
+    <m/>
+    <m/>
+    <m/>
+    <x v="1"/>
+    <x v="1"/>
+    <x v="1"/>
+    <x v="1"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <x v="1"/>
+    <x v="1"/>
+    <x v="1"/>
   </r>
 </pivotCacheRecords>
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0100-000000000000}" name="PivotTable1" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0" dataCaption="Values" itemPrintTitles="1" indent="0" compact="0" outline="1" outlineData="1" compactData="0">
-  <location ref="A5:E10" firstHeaderRow="1" firstDataRow="2" firstDataCol="3" rowPageCount="1" colPageCount="1"/>
-  <pivotFields count="18">
-    <pivotField compact="0" showAll="0"/>
-    <pivotField axis="axisRow" compact="0" showAll="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0100-000000000000}" name="PivotTable1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0" dataCaption="Values" grandTotalCaption="Verfügte Betreuungsgutscheine" updatedVersion="8" itemPrintTitles="1" indent="0" outline="1" outlineData="1" rowHeaderCaption="Filter">
+  <location ref="A8:C15" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
+  <pivotFields count="21">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
       <items count="3">
         <item x="0"/>
         <item x="1"/>
         <item t="default"/>
       </items>
     </pivotField>
-    <pivotField axis="axisRow" compact="0" showAll="0">
+    <pivotField axis="axisRow" showAll="0">
       <items count="3">
         <item x="0"/>
         <item x="1"/>
         <item t="default"/>
       </items>
     </pivotField>
-    <pivotField compact="0" showAll="0"/>
-    <pivotField compact="0" showAll="0"/>
-    <pivotField compact="0" showAll="0"/>
-    <pivotField axis="axisRow" compact="0" showAll="0">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0" includeNewItemsInFilter="1">
       <items count="3">
         <item x="0"/>
         <item x="1"/>
         <item t="default"/>
       </items>
     </pivotField>
-    <pivotField compact="0" showAll="0"/>
-    <pivotField compact="0" showAll="0"/>
-    <pivotField compact="0" showAll="0"/>
-    <pivotField dataField="1" compact="0" showAll="0"/>
-    <pivotField compact="0" showAll="0"/>
-    <pivotField compact="0" showAll="0"/>
-    <pivotField compact="0" showAll="0"/>
-    <pivotField compact="0" showAll="0"/>
-    <pivotField axis="axisPage" compact="0" showAll="0">
+    <pivotField axis="axisRow" showAll="0">
       <items count="3">
         <item x="0"/>
         <item x="1"/>
         <item t="default"/>
       </items>
     </pivotField>
-    <pivotField axis="axisCol" compact="0" showAll="0">
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0" includeNewItemsInFilter="1">
       <items count="3">
         <item x="0"/>
-        <item h="1" x="1"/>
+        <item x="1"/>
         <item t="default"/>
       </items>
     </pivotField>
-    <pivotField compact="0" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisPage" multipleItemSelectionAllowed="1" showAll="0">
+      <items count="4">
+        <item x="0"/>
+        <item h="1" x="1"/>
+        <item h="1" m="1" x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisCol" showAll="0" includeNewItemsInFilter="1">
+      <items count="4">
+        <item m="1" x="2"/>
+        <item x="1"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0" includeNewItemsInFilter="1"/>
   </pivotFields>
-  <rowFields count="3">
-    <field x="1"/>
+  <rowFields count="5">
     <field x="2"/>
-    <field x="6"/>
+    <field x="3"/>
+    <field x="7"/>
+    <field x="8"/>
+    <field x="10"/>
   </rowFields>
+  <rowItems count="6">
+    <i>
+      <x/>
+    </i>
+    <i r="1">
+      <x/>
+    </i>
+    <i r="2">
+      <x/>
+    </i>
+    <i r="3">
+      <x/>
+    </i>
+    <i r="4">
+      <x/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
   <colFields count="1">
-    <field x="16"/>
+    <field x="19"/>
   </colFields>
+  <colItems count="2">
+    <i>
+      <x v="2"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </colItems>
   <pageFields count="1">
-    <pageField fld="15" hier="-1"/>
+    <pageField fld="18" hier="-1"/>
   </pageFields>
   <dataFields count="1">
-    <dataField name="Summe von Betrag in CHF" fld="10" baseField="0" baseItem="0"/>
+    <dataField name="Summe von Betrag in CHF" fld="13" baseField="2" baseItem="0"/>
   </dataFields>
+  <formats count="13">
+    <format dxfId="20">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="5">
+          <reference field="2" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="3" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="7" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="8" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="10" count="1">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="19">
+      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="18">
+      <pivotArea outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="17">
+      <pivotArea type="origin" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="16">
+      <pivotArea type="topRight" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="15">
+      <pivotArea field="2" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
+    </format>
+    <format dxfId="14">
+      <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="13">
+      <pivotArea outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="12">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="18" count="0"/>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="11">
+      <pivotArea field="19" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisCol" fieldPosition="0"/>
+    </format>
+    <format dxfId="10">
+      <pivotArea type="topRight" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="9">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="1">
+          <reference field="19" count="1">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="8">
+      <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
+    </format>
+  </formats>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
   <extLst>
     <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
@@ -1068,63 +1016,128 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0200-000000000000}" name="DataPilot1" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0" dataCaption="Values" itemPrintTitles="1" indent="0" compact="0" outline="1" outlineData="1" compactData="0">
-  <location ref="A6:C9" firstHeaderRow="1" firstDataRow="1" firstDataCol="2" rowPageCount="2" colPageCount="1"/>
-  <pivotFields count="18">
-    <pivotField compact="0" showAll="0"/>
-    <pivotField axis="axisRow" compact="0" showAll="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0200-000000000000}" name="DataPilot1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0" dataCaption="Values" grandTotalCaption="Verfügte Betreuungsgutscheine" updatedVersion="8" itemPrintTitles="1" indent="0" outline="1" outlineData="1" rowHeaderCaption="Filter">
+  <location ref="A9:C14" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
+  <pivotFields count="21">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
       <items count="3">
         <item x="0"/>
         <item x="1"/>
         <item t="default"/>
       </items>
     </pivotField>
-    <pivotField compact="0" showAll="0"/>
-    <pivotField compact="0" showAll="0"/>
-    <pivotField compact="0" showAll="0"/>
-    <pivotField compact="0" showAll="0"/>
-    <pivotField compact="0" showAll="0"/>
-    <pivotField compact="0" showAll="0"/>
-    <pivotField compact="0" showAll="0"/>
-    <pivotField compact="0" showAll="0"/>
-    <pivotField dataField="1" compact="0" showAll="0"/>
-    <pivotField compact="0" showAll="0"/>
-    <pivotField compact="0" showAll="0"/>
-    <pivotField axis="axisRow" compact="0" showAll="0">
+    <pivotField axis="axisRow" showAll="0">
       <items count="3">
         <item x="0"/>
         <item x="1"/>
         <item t="default"/>
       </items>
     </pivotField>
-    <pivotField compact="0" showAll="0"/>
-    <pivotField axis="axisPage" compact="0" showAll="0">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0" includeNewItemsInFilter="1"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
       <items count="3">
         <item x="0"/>
         <item x="1"/>
         <item t="default"/>
       </items>
     </pivotField>
-    <pivotField axis="axisPage" compact="0" showAll="0">
-      <items count="3">
+    <pivotField showAll="0" includeNewItemsInFilter="1"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisPage" showAll="0">
+      <items count="4">
         <item x="0"/>
         <item h="1" x="1"/>
+        <item h="1" m="1" x="2"/>
         <item t="default"/>
       </items>
     </pivotField>
-    <pivotField compact="0" showAll="0"/>
+    <pivotField showAll="0" includeNewItemsInFilter="1"/>
+    <pivotField axis="axisCol" showAll="0" includeNewItemsInFilter="1">
+      <items count="3">
+        <item x="0"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
   </pivotFields>
-  <rowFields count="2">
-    <field x="1"/>
-    <field x="13"/>
+  <rowFields count="3">
+    <field x="2"/>
+    <field x="3"/>
+    <field x="9"/>
   </rowFields>
-  <pageFields count="2">
-    <pageField fld="15" hier="-1"/>
-    <pageField fld="16" hier="-1"/>
+  <rowItems count="4">
+    <i>
+      <x/>
+    </i>
+    <i r="1">
+      <x/>
+    </i>
+    <i r="2">
+      <x/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="20"/>
+  </colFields>
+  <colItems count="2">
+    <i>
+      <x/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </colItems>
+  <pageFields count="1">
+    <pageField fld="18" hier="-1"/>
   </pageFields>
   <dataFields count="1">
-    <dataField name="Zahlungen ausserhalb kiBon" fld="10" baseField="0" baseItem="0"/>
+    <dataField name="Summe von Betrag in CHF" fld="13" baseField="2" baseItem="0"/>
   </dataFields>
+  <formats count="6">
+    <format dxfId="7">
+      <pivotArea outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="6">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="18" count="0"/>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="5">
+      <pivotArea field="20" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisCol" fieldPosition="0"/>
+    </format>
+    <format dxfId="4">
+      <pivotArea type="topRight" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="3">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="1">
+          <reference field="20" count="1">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="2">
+      <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
+    </format>
+  </formats>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
   <extLst>
     <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
@@ -1135,9 +1148,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 – 2022-Design">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 – 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1175,7 +1188,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 – 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -1281,7 +1294,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 – 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1423,7 +1436,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1431,75 +1444,80 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:S11"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:V11"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="21.109375" customWidth="1"/>
-    <col min="2" max="2" width="21.109375" style="57" customWidth="1"/>
-    <col min="3" max="4" width="21.109375" customWidth="1"/>
-    <col min="5" max="5" width="30.88671875" style="1" customWidth="1"/>
-    <col min="6" max="7" width="30.88671875" customWidth="1"/>
-    <col min="8" max="8" width="21.109375" customWidth="1"/>
-    <col min="9" max="10" width="19.44140625" style="57" customWidth="1"/>
-    <col min="11" max="11" width="19.44140625" style="2" customWidth="1"/>
-    <col min="12" max="12" width="16.44140625" style="3" customWidth="1"/>
-    <col min="13" max="13" width="11.44140625" style="4"/>
-    <col min="14" max="14" width="18.88671875" style="4" customWidth="1"/>
-    <col min="15" max="16" width="23.33203125" customWidth="1"/>
-    <col min="17" max="17" width="21.109375" hidden="1" customWidth="1"/>
-    <col min="18" max="18" width="18.88671875" style="4" hidden="1" customWidth="1"/>
+    <col min="1" max="1" width="21.140625" customWidth="1"/>
+    <col min="2" max="2" width="21.140625" style="23" customWidth="1"/>
+    <col min="3" max="4" width="21.140625" customWidth="1"/>
+    <col min="5" max="5" width="30.85546875" style="1" customWidth="1"/>
+    <col min="6" max="7" width="30.85546875" customWidth="1"/>
+    <col min="8" max="8" width="30.85546875" hidden="1" customWidth="1"/>
+    <col min="9" max="9" width="21.140625" customWidth="1"/>
+    <col min="10" max="10" width="19.42578125" style="23" customWidth="1"/>
+    <col min="11" max="11" width="19.42578125" style="23" hidden="1" customWidth="1"/>
+    <col min="12" max="12" width="19.42578125" style="23" customWidth="1"/>
+    <col min="13" max="13" width="19.42578125" style="2" customWidth="1"/>
+    <col min="14" max="14" width="16.42578125" style="3" customWidth="1"/>
+    <col min="15" max="15" width="11.42578125" style="4"/>
+    <col min="16" max="16" width="18.85546875" style="4" customWidth="1"/>
+    <col min="17" max="18" width="23.28515625" customWidth="1"/>
+    <col min="19" max="20" width="21.140625" hidden="1" customWidth="1"/>
+    <col min="21" max="21" width="23.42578125" style="4" hidden="1" customWidth="1"/>
+    <col min="22" max="22" width="12.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" ht="21" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:22" ht="21" x14ac:dyDescent="0.35">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="52"/>
-    </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="B1" s="18"/>
+    </row>
+    <row r="3" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="53"/>
-      <c r="Q3" s="6"/>
-    </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="B3" s="19"/>
+      <c r="S3" s="6"/>
+      <c r="T3" s="6"/>
+    </row>
+    <row r="4" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="54" t="s">
+      <c r="B4" s="20" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="54" t="s">
+      <c r="B5" s="20" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="54" t="s">
+      <c r="B6" s="20" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>8</v>
       </c>
-      <c r="B7" s="54" t="s">
+      <c r="B7" s="20" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="1:19" s="12" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:22" s="12" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="B10" s="55" t="s">
+      <c r="B10" s="21" t="s">
         <v>11</v>
       </c>
       <c r="C10" s="7" t="s">
@@ -1518,105 +1536,131 @@
         <v>14</v>
       </c>
       <c r="H10" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="I10" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="I10" s="55" t="s">
+      <c r="J10" s="21" t="s">
         <v>16</v>
       </c>
-      <c r="J10" s="55" t="s">
+      <c r="K10" s="21" t="s">
+        <v>50</v>
+      </c>
+      <c r="L10" s="21" t="s">
         <v>17</v>
       </c>
-      <c r="K10" s="9" t="s">
+      <c r="M10" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="L10" s="10" t="s">
+      <c r="N10" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="M10" s="7" t="s">
+      <c r="O10" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="N10" s="11" t="s">
+      <c r="P10" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="O10" s="11" t="s">
+      <c r="Q10" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="P10" s="11" t="s">
+      <c r="R10" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="Q10" s="7" t="s">
+      <c r="S10" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="R10" s="11" t="s">
+      <c r="T10" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="U10" s="7" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="11" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A11" s="13" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A11" s="13" t="s">
+      <c r="B11" s="22" t="s">
         <v>26</v>
       </c>
-      <c r="B11" s="56" t="s">
+      <c r="C11" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C11" s="13" t="s">
+      <c r="D11" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="D11" s="13" t="s">
+      <c r="E11" s="14" t="s">
         <v>29</v>
       </c>
-      <c r="E11" s="14" t="s">
+      <c r="F11" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="F11" s="13" t="s">
+      <c r="G11" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="G11" s="13" t="s">
+      <c r="H11" s="13" t="str">
+        <f>CONCATENATE(F11," ",G11)</f>
+        <v>{kindNachname} {kindVorname}</v>
+      </c>
+      <c r="I11" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="H11" s="13" t="s">
+      <c r="J11" s="22" t="s">
         <v>33</v>
       </c>
-      <c r="I11" s="56" t="s">
+      <c r="K11" s="28" t="str">
+        <f>TEXT(J11,"MMM")</f>
+        <v>{zeitabschnittVon}</v>
+      </c>
+      <c r="L11" s="22" t="s">
         <v>34</v>
       </c>
-      <c r="J11" s="56" t="s">
+      <c r="M11" s="15" t="s">
         <v>35</v>
       </c>
-      <c r="K11" s="15" t="s">
+      <c r="N11" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="L11" s="16" t="s">
+      <c r="O11" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="M11" s="17" t="s">
+      <c r="P11" s="17" t="s">
         <v>38</v>
       </c>
-      <c r="N11" s="17" t="s">
+      <c r="Q11" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="O11" s="13" t="s">
+      <c r="R11" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="P11" s="13" t="s">
-        <v>41</v>
-      </c>
-      <c r="Q11" s="13" t="str">
+      <c r="S11" s="13" t="str">
         <f>IF(A11&lt;&gt;"","x","")</f>
         <v>x</v>
       </c>
-      <c r="R11" s="17" t="str">
-        <f>IF(N11="","Ausbezahlt an Institution","Ausserhalb kiBon")</f>
-        <v>Ausserhalb kiBon</v>
-      </c>
-      <c r="S11" s="18" t="s">
-        <v>42</v>
+      <c r="T11" s="13" t="str">
+        <f>IF(P11="X","Abrechnung direkt zwischen Gemeinde &amp; Erziehungsberechtigten","Auszahlung an Institution")</f>
+        <v>Auszahlung an Institution</v>
+      </c>
+      <c r="U11" s="13" t="str">
+        <f>IF(P11="X","Ausserhalb von kiBon","Auszahlung an Institution")</f>
+        <v>Auszahlung an Institution</v>
+      </c>
+      <c r="V11" t="s">
+        <v>41</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A10:N10" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
-  <conditionalFormatting sqref="A11:S11">
-    <cfRule type="expression" dxfId="0" priority="2">
-      <formula>$K11="X"</formula>
+  <autoFilter ref="A10:P10" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <conditionalFormatting sqref="A11:O11 Q11:V11">
+    <cfRule type="expression" dxfId="1" priority="4">
+      <formula>$M11="X"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="P11">
+    <cfRule type="expression" dxfId="0" priority="1">
+      <formula>$L11="X"</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.78749999999999998" bottom="0.78749999999999998" header="0.511811023622047" footer="0.511811023622047"/>
@@ -1626,96 +1670,155 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:E10"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:E15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="26.88671875" customWidth="1"/>
-    <col min="2" max="2" width="22.33203125" customWidth="1"/>
-    <col min="3" max="3" width="26.88671875" customWidth="1"/>
-    <col min="4" max="4" width="24.33203125" customWidth="1"/>
-    <col min="5" max="5" width="13.44140625" customWidth="1"/>
-    <col min="6" max="6" width="16.88671875" customWidth="1"/>
-    <col min="7" max="7" width="13.33203125" customWidth="1"/>
-    <col min="8" max="8" width="25.6640625" customWidth="1"/>
+    <col min="1" max="1" width="26.85546875" style="27" customWidth="1"/>
+    <col min="2" max="2" width="22.28515625" style="27" customWidth="1"/>
+    <col min="3" max="3" width="26.85546875" style="27" customWidth="1"/>
+    <col min="4" max="4" width="24.28515625" style="27" customWidth="1"/>
+    <col min="5" max="5" width="13.42578125" style="27" customWidth="1"/>
+    <col min="6" max="6" width="16.85546875" style="27" customWidth="1"/>
+    <col min="7" max="7" width="13.28515625" style="27" customWidth="1"/>
+    <col min="8" max="8" width="25.7109375" style="27" customWidth="1"/>
+    <col min="9" max="16384" width="11.42578125" style="27"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A1" s="19" t="s">
+    <row r="1" spans="1:5" customFormat="1" ht="21" x14ac:dyDescent="0.35">
+      <c r="A1" s="30" t="s">
+        <v>52</v>
+      </c>
+      <c r="B1" s="32"/>
+      <c r="C1" s="32"/>
+      <c r="D1" s="32"/>
+      <c r="E1" s="36"/>
+    </row>
+    <row r="2" spans="1:5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="31" t="s">
+        <v>57</v>
+      </c>
+      <c r="B2" s="32"/>
+      <c r="C2" s="32"/>
+      <c r="D2" s="32"/>
+      <c r="E2" s="36"/>
+    </row>
+    <row r="3" spans="1:5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="31" t="s">
+        <v>58</v>
+      </c>
+      <c r="B3" s="32"/>
+      <c r="C3" s="32"/>
+      <c r="D3" s="32"/>
+      <c r="E3" s="36"/>
+    </row>
+    <row r="4" spans="1:5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="31" t="s">
+        <v>56</v>
+      </c>
+      <c r="B4" s="32"/>
+      <c r="C4" s="32"/>
+      <c r="D4" s="32"/>
+      <c r="E4" s="36"/>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" s="33"/>
+      <c r="B5" s="32"/>
+      <c r="C5" s="32"/>
+      <c r="D5" s="32"/>
+      <c r="E5" s="32"/>
+    </row>
+    <row r="6" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="29" t="s">
+        <v>24</v>
+      </c>
+      <c r="B6" s="27" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="3" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="20" t="s">
-        <v>23</v>
-      </c>
-      <c r="B3" s="13" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A5" s="21" t="s">
-        <v>45</v>
-      </c>
-      <c r="B5" s="22"/>
-      <c r="C5" s="23"/>
-      <c r="D5" s="24" t="s">
-        <v>24</v>
-      </c>
-      <c r="E5" s="25"/>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A6" s="26" t="s">
-        <v>11</v>
-      </c>
-      <c r="B6" s="27" t="s">
-        <v>4</v>
-      </c>
-      <c r="C6" s="27" t="s">
-        <v>14</v>
-      </c>
-      <c r="D6" s="28" t="s">
+    <row r="8" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="29" t="s">
+        <v>42</v>
+      </c>
+      <c r="B8" s="29" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="29" t="s">
+        <v>49</v>
+      </c>
+      <c r="B9" s="27" t="s">
+        <v>53</v>
+      </c>
+      <c r="C9" s="27" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" s="34" t="s">
+        <v>27</v>
+      </c>
+      <c r="B10" s="27">
+        <v>0</v>
+      </c>
+      <c r="C10" s="27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" s="34" t="s">
+        <v>28</v>
+      </c>
+      <c r="B11" s="27">
+        <v>0</v>
+      </c>
+      <c r="C11" s="27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="A12" s="34" t="s">
         <v>46</v>
       </c>
-      <c r="E6" s="29" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A7" s="30" t="s">
-        <v>27</v>
-      </c>
-      <c r="B7" s="31"/>
-      <c r="C7" s="32"/>
-      <c r="D7" s="33"/>
-      <c r="E7" s="34"/>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A8" s="35"/>
-      <c r="B8" s="36" t="s">
-        <v>28</v>
-      </c>
-      <c r="C8" s="36"/>
-      <c r="D8" s="37"/>
-      <c r="E8" s="38"/>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A9" s="39"/>
-      <c r="B9" s="40"/>
-      <c r="C9" s="40" t="s">
+      <c r="B12" s="27">
+        <v>0</v>
+      </c>
+      <c r="C12" s="27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" s="34" t="s">
         <v>32</v>
       </c>
-      <c r="D9" s="41"/>
-      <c r="E9" s="42"/>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A10" s="43" t="s">
-        <v>47</v>
-      </c>
-      <c r="B10" s="44"/>
-      <c r="C10" s="45"/>
-      <c r="D10" s="46"/>
-      <c r="E10" s="47"/>
+      <c r="B13" s="27">
+        <v>0</v>
+      </c>
+      <c r="C13" s="27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14" s="35" t="s">
+        <v>33</v>
+      </c>
+      <c r="B14" s="27">
+        <v>0</v>
+      </c>
+      <c r="C14" s="27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="A15" s="34" t="s">
+        <v>48</v>
+      </c>
+      <c r="B15" s="27">
+        <v>0</v>
+      </c>
+      <c r="C15" s="27">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.78749999999999998" bottom="0.78749999999999998" header="0.511811023622047" footer="0.511811023622047"/>
@@ -1725,75 +1828,124 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:C9"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:D14"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="21" customWidth="1"/>
-    <col min="2" max="2" width="24.77734375" customWidth="1"/>
-    <col min="3" max="3" width="7.6640625" customWidth="1"/>
-    <col min="4" max="4" width="25.6640625" customWidth="1"/>
-    <col min="5" max="5" width="13.44140625" customWidth="1"/>
-    <col min="6" max="6" width="16.88671875" customWidth="1"/>
-    <col min="7" max="7" width="13.33203125" customWidth="1"/>
-    <col min="8" max="8" width="25.6640625" customWidth="1"/>
+    <col min="2" max="4" width="22.85546875" style="27" customWidth="1"/>
+    <col min="5" max="5" width="13.42578125" customWidth="1"/>
+    <col min="6" max="6" width="16.85546875" customWidth="1"/>
+    <col min="7" max="7" width="13.28515625" customWidth="1"/>
+    <col min="8" max="8" width="25.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A1" s="19" t="s">
+    <row r="1" spans="1:4" ht="21" x14ac:dyDescent="0.35">
+      <c r="A1" s="30" t="s">
+        <v>51</v>
+      </c>
+      <c r="B1" s="37"/>
+      <c r="C1" s="37"/>
+      <c r="D1" s="37"/>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" s="31" t="s">
+        <v>59</v>
+      </c>
+      <c r="B2" s="37"/>
+      <c r="C2" s="37"/>
+      <c r="D2" s="37"/>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" s="31" t="s">
+        <v>60</v>
+      </c>
+      <c r="B3" s="37"/>
+      <c r="C3" s="37"/>
+      <c r="D3" s="37"/>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" s="31" t="s">
+        <v>61</v>
+      </c>
+      <c r="B4" s="37"/>
+      <c r="C4" s="37"/>
+      <c r="D4" s="37"/>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" s="6"/>
+    </row>
+    <row r="6" spans="1:4" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="7" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="24" t="s">
+        <v>24</v>
+      </c>
+      <c r="B7" s="27" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="9" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="24" t="s">
+        <v>42</v>
+      </c>
+      <c r="B9" s="29" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="51.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="24" t="s">
+        <v>49</v>
+      </c>
+      <c r="B10" s="27" t="s">
+        <v>53</v>
+      </c>
+      <c r="C10" s="27" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" s="6"/>
-    </row>
-    <row r="3" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="20" t="s">
-        <v>23</v>
-      </c>
-      <c r="B3" s="13" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="20" t="s">
-        <v>24</v>
-      </c>
-      <c r="B4" s="13" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A6" s="48" t="s">
-        <v>11</v>
-      </c>
-      <c r="B6" s="24" t="s">
-        <v>21</v>
-      </c>
-      <c r="C6" s="49" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A7" s="30" t="s">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="B7" s="36"/>
-      <c r="C7" s="50"/>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A8" s="39"/>
-      <c r="B8" s="40" t="s">
-        <v>39</v>
-      </c>
-      <c r="C8" s="51"/>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A9" s="43" t="s">
-        <v>47</v>
-      </c>
-      <c r="B9" s="45"/>
-      <c r="C9" s="47"/>
+      <c r="B11" s="27">
+        <v>0</v>
+      </c>
+      <c r="C11" s="27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" s="25" t="s">
+        <v>28</v>
+      </c>
+      <c r="B12" s="27">
+        <v>0</v>
+      </c>
+      <c r="C12" s="27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" s="26" t="s">
+        <v>33</v>
+      </c>
+      <c r="B13" s="27">
+        <v>0</v>
+      </c>
+      <c r="C13" s="27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="B14" s="27">
+        <v>0</v>
+      </c>
+      <c r="C14" s="27">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.78749999999999998" bottom="0.78749999999999998" header="0.511811023622047" footer="0.511811023622047"/>

--- a/ebegu-server/src/main/resources/reporting/Zahlungen_DE.xlsx
+++ b/ebegu-server/src/main/resources/reporting/Zahlungen_DE.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27830"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\java\kibon\ebegu-server\src\main\resources\reporting\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aese\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7129528D-351C-44E0-AF8F-3C98A3B6A5F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C0C6879-299A-42DA-9571-DA89C0497D1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15840" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="-16320" windowWidth="29040" windowHeight="15720" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="1" r:id="rId1"/>
@@ -18,10 +18,10 @@
     <sheet name="Auszahlung nach Gemeinde" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Data!$A$10:$P$10</definedName>
-    <definedName name="data">Data!$A$10:$R$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Data!$A$12:$Q$12</definedName>
+    <definedName name="data">Data!$A$12:$S$13</definedName>
   </definedNames>
-  <calcPr calcId="191029" iterateDelta="1E-4"/>
+  <calcPr calcId="191029"/>
   <pivotCaches>
     <pivotCache cacheId="0" r:id="rId4"/>
   </pivotCaches>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="64">
   <si>
     <t>Zahlungen</t>
   </si>
@@ -197,9 +197,6 @@
     <t>Filter</t>
   </si>
   <si>
-    <t>Monat</t>
-  </si>
-  <si>
     <t>Übersicht Auszahlungen: nach Gemeinde</t>
   </si>
   <si>
@@ -213,6 +210,19 @@
   </si>
   <si>
     <t>Auszahlung an (für Kind Pivot)</t>
+  </si>
+  <si>
+    <r>
+      <t>Auszahlung an Institution:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Betrag, der von der Gemeinde an die Institution überwiesen wurde. Der Betrag beinhaltet Korrekturen, welche in den Zahlungslauf mit der Institution übernommen wurden. Dieser Betrag wird in der Rechnung an die Antragstellenden von den Vollkosten abgezogen.</t>
+    </r>
   </si>
   <si>
     <r>
@@ -224,12 +234,12 @@
         <rFont val="Calibri"/>
         <family val="2"/>
       </rPr>
-      <t>Höhe des Betreuungsgutscheins pro Kind und Monat gemäss der aktuell gültigen Verfügung. Der Betrag beinhaltet Korrekturen, welche in den Zahlungslauf mit der Institution übernommen wurden, so wie auch Zahlungen, die nicht in den Zahlungslauf mit der Institution übernommen wurden und direkt zwischen Gemeinde und Erziehungsberechtigten abgerechnet werden.</t>
+      <t>Höhe des Betreuungsgutscheins pro Kind und Monat gemäss der aktuell gültigen Verfügung. Der Betrag beinhaltet Korrekturen, welche in den Zahlungslauf mit der Institution übernommen wurden, so wie auch Zahlungen, die nicht in den Zahlungslauf mit der Institution übernommen wurden und direkt zwischen Gemeinde und Antragstellenden abgerechnet werden.</t>
     </r>
   </si>
   <si>
     <r>
-      <t>Auszahlung an Institution:</t>
+      <t>Abrechnung direkt zwischen Gemeinde &amp; Antragstellenden:</t>
     </r>
     <r>
       <rPr>
@@ -237,70 +247,35 @@
         <rFont val="Calibri"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve"> Betrag, der von der Gemeinde an die Institution überwiesen wurde. Der Betrag beinhaltet Korrekturen, welche in den Zahlungslauf mit der Institution übernommen wurden. Dieser Betrag wird in der Rechnung an die Erziehungsberechtigten von den Vollkosten abgezogen.</t>
+      <t xml:space="preserve"> Korrekturbetrag zum effektiven Gutschein. Entspricht dem Differenzbetrag von dem an die Institution ausbezahlten Betrag und dem aktuell gültigen Betreuungsgutschein. Dieser Korrekturbetrag wird ausserhalb von kiBon von der Gemeinde direkt mit den Antragstellenden beglichen.</t>
     </r>
   </si>
   <si>
-    <r>
-      <t>Abrechnung direkt zwischen Gemeinde &amp; Erziehungsberechtigten:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> Korrekturbetrag zum effektiven Gutschein. Entspricht dem Differenzbetrag von dem an die Institution ausbezahlten Betrag und dem aktuell gültigen Betreuungsgutschein. Dieser Korrekturbetrag wird ausserhalb von kiBon von der Gemeinde direkt mit den Erziehungsberechtigten beglichen.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Auszahlung an Institution:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> Betrag, der von der Gemeinde an die Institution überwiesen wurde. Wird in der Rechnung an die Erziehungsberechtigten von den Vollkosten abgezogen.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Ausserhalb von kiBon: </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>Korrekturbetrag, welcher ausserhalb von kiBon von der Gemeinde direkt mit den Erziehungsberechtigten beglichen wird. Differenzbetrag von dem an die Institution ausbezahlten Betrag und dem aktuell gültigen Betreuungsgutschein.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Verfügte Betreuungsgutscheine: </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>Höhe des Betreuungsgutscheins pro Kind und Monat gemäss der aktuell gültigen Verfügung.</t>
-    </r>
+    <t>Von</t>
+  </si>
+  <si>
+    <t>Bis</t>
+  </si>
+  <si>
+    <t>{bisParam}</t>
+  </si>
+  <si>
+    <t>{vonParam}</t>
+  </si>
+  <si>
+    <t>Monat</t>
+  </si>
+  <si>
+    <t>Jahr</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="m/d/yyyy\ h:mm"/>
     <numFmt numFmtId="165" formatCode="&quot;CHF &quot;#,##0.00"/>
-    <numFmt numFmtId="166" formatCode="mmm"/>
   </numFmts>
   <fonts count="9" x14ac:knownFonts="1">
     <font>
@@ -429,7 +404,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyBorder="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -482,7 +457,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -497,12 +471,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" indent="3"/>
     </xf>
   </cellXfs>
   <cellStyles count="9">
@@ -516,7 +490,7 @@
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
     <cellStyle name="Standard 2" xfId="8" xr:uid="{00000000-0005-0000-0000-00000D000000}"/>
   </cellStyles>
-  <dxfs count="21">
+  <dxfs count="20">
     <dxf>
       <font>
         <color rgb="FFFF0000"/>
@@ -580,9 +554,6 @@
     </dxf>
     <dxf>
       <alignment wrapText="1" indent="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="mmm"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -666,11 +637,11 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Brunner Anita" refreshedDate="45519.518409027776" createdVersion="3" refreshedVersion="8" recordCount="2" xr:uid="{00000000-000A-0000-FFFF-FFFF01000000}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Aeschlimann Severin" refreshedDate="45988.463295370369" createdVersion="3" refreshedVersion="8" recordCount="2" xr:uid="{00000000-000A-0000-FFFF-FFFF01000000}">
   <cacheSource type="worksheet">
-    <worksheetSource ref="A10:U1048576" sheet="Data"/>
+    <worksheetSource ref="A12:V1048576" sheet="Data"/>
   </cacheSource>
-  <cacheFields count="21">
+  <cacheFields count="22">
     <cacheField name="Titel Zahlungslauf" numFmtId="0">
       <sharedItems containsBlank="1"/>
     </cacheField>
@@ -711,12 +682,15 @@
       </sharedItems>
     </cacheField>
     <cacheField name="von" numFmtId="14">
+      <sharedItems containsBlank="1"/>
+    </cacheField>
+    <cacheField name="Monat" numFmtId="14">
       <sharedItems containsBlank="1" count="2">
         <s v="{zeitabschnittVon}"/>
         <m/>
       </sharedItems>
     </cacheField>
-    <cacheField name="Monat" numFmtId="0">
+    <cacheField name="Jahr" numFmtId="0">
       <sharedItems containsBlank="1" count="2">
         <s v="{zeitabschnittVon}"/>
         <m/>
@@ -784,6 +758,7 @@
     <s v="{kindVorname}"/>
     <x v="0"/>
     <x v="0"/>
+    <s v="{zeitabschnittVon}"/>
     <x v="0"/>
     <x v="0"/>
     <s v="{zeitabschnittBis}"/>
@@ -807,6 +782,7 @@
     <m/>
     <x v="1"/>
     <x v="1"/>
+    <m/>
     <x v="1"/>
     <x v="1"/>
     <m/>
@@ -825,8 +801,8 @@
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0100-000000000000}" name="PivotTable1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0" dataCaption="Values" grandTotalCaption="Verfügte Betreuungsgutscheine" updatedVersion="8" itemPrintTitles="1" indent="0" outline="1" outlineData="1" rowHeaderCaption="Filter">
-  <location ref="A8:C15" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
-  <pivotFields count="21">
+  <location ref="A8:C16" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
+  <pivotFields count="22">
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField axis="axisRow" showAll="0">
@@ -861,6 +837,13 @@
       </items>
     </pivotField>
     <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0" includeNewItemsInFilter="1" sortType="ascending">
+      <items count="3">
+        <item x="0"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
     <pivotField axis="axisRow" showAll="0" includeNewItemsInFilter="1">
       <items count="3">
         <item x="0"/>
@@ -893,14 +876,15 @@
     </pivotField>
     <pivotField showAll="0" includeNewItemsInFilter="1"/>
   </pivotFields>
-  <rowFields count="5">
+  <rowFields count="6">
     <field x="2"/>
     <field x="3"/>
     <field x="7"/>
     <field x="8"/>
+    <field x="11"/>
     <field x="10"/>
   </rowFields>
-  <rowItems count="6">
+  <rowItems count="7">
     <i>
       <x/>
     </i>
@@ -916,12 +900,15 @@
     <i r="4">
       <x/>
     </i>
+    <i r="5">
+      <x/>
+    </i>
     <i t="grand">
       <x/>
     </i>
   </rowItems>
   <colFields count="1">
-    <field x="19"/>
+    <field x="20"/>
   </colFields>
   <colItems count="2">
     <i>
@@ -932,33 +919,12 @@
     </i>
   </colItems>
   <pageFields count="1">
-    <pageField fld="18" hier="-1"/>
+    <pageField fld="19" hier="-1"/>
   </pageFields>
   <dataFields count="1">
-    <dataField name="Summe von Betrag in CHF" fld="13" baseField="2" baseItem="0"/>
+    <dataField name="Summe von Betrag in CHF" fld="14" baseField="2" baseItem="0"/>
   </dataFields>
-  <formats count="13">
-    <format dxfId="20">
-      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
-        <references count="5">
-          <reference field="2" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="3" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="7" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="8" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="10" count="1">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
+  <formats count="12">
     <format dxfId="19">
       <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
     </format>
@@ -983,12 +949,12 @@
     <format dxfId="12">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
-          <reference field="18" count="0"/>
+          <reference field="19" count="0"/>
         </references>
       </pivotArea>
     </format>
     <format dxfId="11">
-      <pivotArea field="19" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisCol" fieldPosition="0"/>
+      <pivotArea field="20" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisCol" fieldPosition="0"/>
     </format>
     <format dxfId="10">
       <pivotArea type="topRight" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
@@ -996,7 +962,7 @@
     <format dxfId="9">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
-          <reference field="19" count="1">
+          <reference field="20" count="1">
             <x v="2"/>
           </reference>
         </references>
@@ -1017,8 +983,8 @@
 
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0200-000000000000}" name="DataPilot1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0" dataCaption="Values" grandTotalCaption="Verfügte Betreuungsgutscheine" updatedVersion="8" itemPrintTitles="1" indent="0" outline="1" outlineData="1" rowHeaderCaption="Filter">
-  <location ref="A9:C14" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
-  <pivotFields count="21">
+  <location ref="A9:C15" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
+  <pivotFields count="22">
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField axis="axisRow" showAll="0">
@@ -1040,14 +1006,21 @@
     <pivotField showAll="0"/>
     <pivotField showAll="0" includeNewItemsInFilter="1"/>
     <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0" includeNewItemsInFilter="1">
       <items count="3">
         <item x="0"/>
         <item x="1"/>
         <item t="default"/>
       </items>
     </pivotField>
-    <pivotField showAll="0" includeNewItemsInFilter="1"/>
+    <pivotField axis="axisRow" showAll="0" includeNewItemsInFilter="1">
+      <items count="3">
+        <item x="0"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField dataField="1" showAll="0"/>
@@ -1072,12 +1045,13 @@
       </items>
     </pivotField>
   </pivotFields>
-  <rowFields count="3">
+  <rowFields count="4">
     <field x="2"/>
     <field x="3"/>
-    <field x="9"/>
+    <field x="11"/>
+    <field x="10"/>
   </rowFields>
-  <rowItems count="4">
+  <rowItems count="5">
     <i>
       <x/>
     </i>
@@ -1087,12 +1061,15 @@
     <i r="2">
       <x/>
     </i>
+    <i r="3">
+      <x/>
+    </i>
     <i t="grand">
       <x/>
     </i>
   </rowItems>
   <colFields count="1">
-    <field x="20"/>
+    <field x="21"/>
   </colFields>
   <colItems count="2">
     <i>
@@ -1103,10 +1080,10 @@
     </i>
   </colItems>
   <pageFields count="1">
-    <pageField fld="18" hier="-1"/>
+    <pageField fld="19" hier="-1"/>
   </pageFields>
   <dataFields count="1">
-    <dataField name="Summe von Betrag in CHF" fld="13" baseField="2" baseItem="0"/>
+    <dataField name="Summe von Betrag in CHF" fld="14" baseField="2" baseItem="0"/>
   </dataFields>
   <formats count="6">
     <format dxfId="7">
@@ -1115,12 +1092,12 @@
     <format dxfId="6">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
-          <reference field="18" count="0"/>
+          <reference field="19" count="0"/>
         </references>
       </pivotArea>
     </format>
     <format dxfId="5">
-      <pivotArea field="20" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisCol" fieldPosition="0"/>
+      <pivotArea field="21" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisCol" fieldPosition="0"/>
     </format>
     <format dxfId="4">
       <pivotArea type="topRight" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
@@ -1128,7 +1105,7 @@
     <format dxfId="3">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
-          <reference field="20" count="1">
+          <reference field="21" count="1">
             <x v="0"/>
           </reference>
         </references>
@@ -1444,7 +1421,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:V11"/>
+  <dimension ref="A1:W13"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="21.140625" customWidth="1"/>
@@ -1452,36 +1429,37 @@
     <col min="3" max="4" width="21.140625" customWidth="1"/>
     <col min="5" max="5" width="30.85546875" style="1" customWidth="1"/>
     <col min="6" max="7" width="30.85546875" customWidth="1"/>
-    <col min="8" max="8" width="30.85546875" hidden="1" customWidth="1"/>
+    <col min="8" max="8" width="14.140625" hidden="1" customWidth="1"/>
     <col min="9" max="9" width="21.140625" customWidth="1"/>
     <col min="10" max="10" width="19.42578125" style="23" customWidth="1"/>
-    <col min="11" max="11" width="19.42578125" style="23" hidden="1" customWidth="1"/>
-    <col min="12" max="12" width="19.42578125" style="23" customWidth="1"/>
-    <col min="13" max="13" width="19.42578125" style="2" customWidth="1"/>
-    <col min="14" max="14" width="16.42578125" style="3" customWidth="1"/>
-    <col min="15" max="15" width="11.42578125" style="4"/>
-    <col min="16" max="16" width="18.85546875" style="4" customWidth="1"/>
-    <col min="17" max="18" width="23.28515625" customWidth="1"/>
-    <col min="19" max="20" width="21.140625" hidden="1" customWidth="1"/>
-    <col min="21" max="21" width="23.42578125" style="4" hidden="1" customWidth="1"/>
-    <col min="22" max="22" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.140625" style="23" hidden="1" customWidth="1"/>
+    <col min="12" max="12" width="13.7109375" style="23" hidden="1" customWidth="1"/>
+    <col min="13" max="13" width="19.42578125" style="23" customWidth="1"/>
+    <col min="14" max="14" width="19.42578125" style="2" customWidth="1"/>
+    <col min="15" max="15" width="16.42578125" style="3" customWidth="1"/>
+    <col min="16" max="16" width="11.42578125" style="4"/>
+    <col min="17" max="17" width="18.85546875" style="4" customWidth="1"/>
+    <col min="18" max="19" width="23.28515625" customWidth="1"/>
+    <col min="20" max="21" width="21.140625" hidden="1" customWidth="1"/>
+    <col min="22" max="22" width="23.42578125" style="4" hidden="1" customWidth="1"/>
+    <col min="23" max="23" width="12.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" ht="21" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:23" ht="21" x14ac:dyDescent="0.35">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="18"/>
     </row>
-    <row r="3" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
         <v>1</v>
       </c>
       <c r="B3" s="19"/>
-      <c r="S3" s="6"/>
       <c r="T3" s="6"/>
-    </row>
-    <row r="4" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="U3" s="6"/>
+    </row>
+    <row r="4" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>2</v>
       </c>
@@ -1489,7 +1467,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -1497,7 +1475,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -1505,7 +1483,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -1513,154 +1491,181 @@
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="1:22" s="12" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A10" s="7" t="s">
+    <row r="8" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>58</v>
+      </c>
+      <c r="B8" s="20" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="9" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>59</v>
+      </c>
+      <c r="B9" s="20" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="12" spans="1:23" s="12" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A12" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="B10" s="21" t="s">
+      <c r="B12" s="21" t="s">
         <v>11</v>
       </c>
-      <c r="C10" s="7" t="s">
+      <c r="C12" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="D10" s="7" t="s">
+      <c r="D12" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="E10" s="8" t="s">
+      <c r="E12" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="F10" s="7" t="s">
+      <c r="F12" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="G10" s="7" t="s">
+      <c r="G12" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="H10" s="7" t="s">
+      <c r="H12" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="I10" s="7" t="s">
+      <c r="I12" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="J10" s="21" t="s">
+      <c r="J12" s="21" t="s">
         <v>16</v>
       </c>
-      <c r="K10" s="21" t="s">
-        <v>50</v>
-      </c>
-      <c r="L10" s="21" t="s">
+      <c r="K12" s="21" t="s">
+        <v>62</v>
+      </c>
+      <c r="L12" s="21" t="s">
+        <v>63</v>
+      </c>
+      <c r="M12" s="21" t="s">
         <v>17</v>
       </c>
-      <c r="M10" s="9" t="s">
+      <c r="N12" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="N10" s="10" t="s">
+      <c r="O12" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="O10" s="7" t="s">
+      <c r="P12" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="P10" s="11" t="s">
+      <c r="Q12" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="Q10" s="11" t="s">
+      <c r="R12" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="R10" s="11" t="s">
+      <c r="S12" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="S10" s="7" t="s">
+      <c r="T12" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="T10" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="U10" s="7" t="s">
+      <c r="U12" s="7" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A11" s="13" t="s">
+      <c r="V12" s="7" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="13" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A13" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="B11" s="22" t="s">
+      <c r="B13" s="22" t="s">
         <v>26</v>
       </c>
-      <c r="C11" s="13" t="s">
+      <c r="C13" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="D11" s="13" t="s">
+      <c r="D13" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="E11" s="14" t="s">
+      <c r="E13" s="14" t="s">
         <v>29</v>
       </c>
-      <c r="F11" s="13" t="s">
+      <c r="F13" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="G11" s="13" t="s">
+      <c r="G13" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="H11" s="13" t="str">
-        <f>CONCATENATE(F11," ",G11)</f>
+      <c r="H13" s="13" t="str">
+        <f>CONCATENATE(F13," ",G13)</f>
         <v>{kindNachname} {kindVorname}</v>
       </c>
-      <c r="I11" s="13" t="s">
+      <c r="I13" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="J11" s="22" t="s">
+      <c r="J13" s="22" t="s">
         <v>33</v>
       </c>
-      <c r="K11" s="28" t="str">
-        <f>TEXT(J11,"MMM")</f>
+      <c r="K13" s="22" t="str">
+        <f>TEXT(J13,"MMM")</f>
         <v>{zeitabschnittVon}</v>
       </c>
-      <c r="L11" s="22" t="s">
+      <c r="L13" s="13" t="e">
+        <f>YEAR(J13)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="M13" s="22" t="s">
         <v>34</v>
       </c>
-      <c r="M11" s="15" t="s">
+      <c r="N13" s="15" t="s">
         <v>35</v>
       </c>
-      <c r="N11" s="16" t="s">
+      <c r="O13" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="O11" s="17" t="s">
+      <c r="P13" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="P11" s="17" t="s">
+      <c r="Q13" s="17" t="s">
         <v>38</v>
       </c>
-      <c r="Q11" s="13" t="s">
+      <c r="R13" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="R11" s="13" t="s">
+      <c r="S13" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="S11" s="13" t="str">
-        <f>IF(A11&lt;&gt;"","x","")</f>
+      <c r="T13" s="13" t="str">
+        <f>IF(A13&lt;&gt;"","x","")</f>
         <v>x</v>
       </c>
-      <c r="T11" s="13" t="str">
-        <f>IF(P11="X","Abrechnung direkt zwischen Gemeinde &amp; Erziehungsberechtigten","Auszahlung an Institution")</f>
+      <c r="U13" s="13" t="str">
+        <f>IF(Q13="X","Abrechnung direkt zwischen Gemeinde &amp; Erziehungsberechtigten","Auszahlung an Institution")</f>
         <v>Auszahlung an Institution</v>
       </c>
-      <c r="U11" s="13" t="str">
-        <f>IF(P11="X","Ausserhalb von kiBon","Auszahlung an Institution")</f>
+      <c r="V13" s="13" t="str">
+        <f>IF(Q13="X","Ausserhalb von kiBon","Auszahlung an Institution")</f>
         <v>Auszahlung an Institution</v>
       </c>
-      <c r="V11" t="s">
+      <c r="W13" t="s">
         <v>41</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A10:P10" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
-  <conditionalFormatting sqref="A11:O11 Q11:V11">
+  <autoFilter ref="A12:Q12" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A13:W13">
+    <sortCondition ref="I13"/>
+    <sortCondition ref="J13"/>
+  </sortState>
+  <conditionalFormatting sqref="A13:P13 R13:W13">
     <cfRule type="expression" dxfId="1" priority="4">
-      <formula>$M11="X"</formula>
+      <formula>$N13="X"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P11">
+  <conditionalFormatting sqref="Q13">
     <cfRule type="expression" dxfId="0" priority="1">
-      <formula>$L11="X"</formula>
+      <formula>$M13="X"</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.78749999999999998" bottom="0.78749999999999998" header="0.511811023622047" footer="0.511811023622047"/>
@@ -1670,7 +1675,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:E15"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="26.85546875" style="27" customWidth="1"/>
@@ -1685,50 +1690,50 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" customFormat="1" ht="21" x14ac:dyDescent="0.35">
-      <c r="A1" s="30" t="s">
-        <v>52</v>
-      </c>
-      <c r="B1" s="32"/>
-      <c r="C1" s="32"/>
-      <c r="D1" s="32"/>
-      <c r="E1" s="36"/>
+      <c r="A1" s="29" t="s">
+        <v>51</v>
+      </c>
+      <c r="B1" s="31"/>
+      <c r="C1" s="31"/>
+      <c r="D1" s="31"/>
+      <c r="E1" s="34"/>
     </row>
     <row r="2" spans="1:5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="31" t="s">
+      <c r="A2" s="30" t="s">
+        <v>55</v>
+      </c>
+      <c r="B2" s="31"/>
+      <c r="C2" s="31"/>
+      <c r="D2" s="31"/>
+      <c r="E2" s="34"/>
+    </row>
+    <row r="3" spans="1:5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="30" t="s">
         <v>57</v>
       </c>
-      <c r="B2" s="32"/>
-      <c r="C2" s="32"/>
-      <c r="D2" s="32"/>
-      <c r="E2" s="36"/>
-    </row>
-    <row r="3" spans="1:5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="31" t="s">
-        <v>58</v>
-      </c>
-      <c r="B3" s="32"/>
-      <c r="C3" s="32"/>
-      <c r="D3" s="32"/>
-      <c r="E3" s="36"/>
+      <c r="B3" s="31"/>
+      <c r="C3" s="31"/>
+      <c r="D3" s="31"/>
+      <c r="E3" s="34"/>
     </row>
     <row r="4" spans="1:5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="31" t="s">
+      <c r="A4" s="30" t="s">
         <v>56</v>
       </c>
-      <c r="B4" s="32"/>
-      <c r="C4" s="32"/>
-      <c r="D4" s="32"/>
-      <c r="E4" s="36"/>
+      <c r="B4" s="31"/>
+      <c r="C4" s="31"/>
+      <c r="D4" s="31"/>
+      <c r="E4" s="34"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="33"/>
-      <c r="B5" s="32"/>
-      <c r="C5" s="32"/>
-      <c r="D5" s="32"/>
-      <c r="E5" s="32"/>
+      <c r="A5" s="32"/>
+      <c r="B5" s="31"/>
+      <c r="C5" s="31"/>
+      <c r="D5" s="31"/>
+      <c r="E5" s="31"/>
     </row>
     <row r="6" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="29" t="s">
+      <c r="A6" s="28" t="s">
         <v>24</v>
       </c>
       <c r="B6" s="27" t="s">
@@ -1736,26 +1741,26 @@
       </c>
     </row>
     <row r="8" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="29" t="s">
+      <c r="A8" s="28" t="s">
         <v>42</v>
       </c>
-      <c r="B8" s="29" t="s">
+      <c r="B8" s="28" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="29" t="s">
+      <c r="A9" s="28" t="s">
         <v>49</v>
       </c>
       <c r="B9" s="27" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C9" s="27" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" s="34" t="s">
+      <c r="A10" s="33" t="s">
         <v>27</v>
       </c>
       <c r="B10" s="27">
@@ -1766,7 +1771,7 @@
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" s="34" t="s">
+      <c r="A11" s="33" t="s">
         <v>28</v>
       </c>
       <c r="B11" s="27">
@@ -1777,7 +1782,7 @@
       </c>
     </row>
     <row r="12" spans="1:5" ht="30" x14ac:dyDescent="0.25">
-      <c r="A12" s="34" t="s">
+      <c r="A12" s="33" t="s">
         <v>46</v>
       </c>
       <c r="B12" s="27">
@@ -1788,7 +1793,7 @@
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13" s="34" t="s">
+      <c r="A13" s="33" t="s">
         <v>32</v>
       </c>
       <c r="B13" s="27">
@@ -1799,7 +1804,7 @@
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A14" s="35" t="s">
+      <c r="A14" s="33" t="s">
         <v>33</v>
       </c>
       <c r="B14" s="27">
@@ -1809,14 +1814,25 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:5" ht="30" x14ac:dyDescent="0.25">
-      <c r="A15" s="34" t="s">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15" s="33" t="s">
+        <v>33</v>
+      </c>
+      <c r="B15" s="27">
+        <v>0</v>
+      </c>
+      <c r="C15" s="27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="A16" s="33" t="s">
         <v>48</v>
       </c>
-      <c r="B15" s="27">
-        <v>0</v>
-      </c>
-      <c r="C15" s="27">
+      <c r="B16" s="27">
+        <v>0</v>
+      </c>
+      <c r="C16" s="27">
         <v>0</v>
       </c>
     </row>
@@ -1828,7 +1844,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:D14"/>
+  <dimension ref="A1:D15"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="21" customWidth="1"/>
@@ -1840,36 +1856,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="21" x14ac:dyDescent="0.35">
-      <c r="A1" s="30" t="s">
-        <v>51</v>
-      </c>
-      <c r="B1" s="37"/>
-      <c r="C1" s="37"/>
-      <c r="D1" s="37"/>
+      <c r="A1" s="29" t="s">
+        <v>50</v>
+      </c>
+      <c r="B1" s="35"/>
+      <c r="C1" s="35"/>
+      <c r="D1" s="35"/>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" s="31" t="s">
-        <v>59</v>
-      </c>
-      <c r="B2" s="37"/>
-      <c r="C2" s="37"/>
-      <c r="D2" s="37"/>
+      <c r="A2" s="30" t="s">
+        <v>55</v>
+      </c>
+      <c r="B2" s="35"/>
+      <c r="C2" s="35"/>
+      <c r="D2" s="35"/>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" s="31" t="s">
-        <v>60</v>
-      </c>
-      <c r="B3" s="37"/>
-      <c r="C3" s="37"/>
-      <c r="D3" s="37"/>
+      <c r="A3" s="30" t="s">
+        <v>57</v>
+      </c>
+      <c r="B3" s="35"/>
+      <c r="C3" s="35"/>
+      <c r="D3" s="35"/>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" s="31" t="s">
-        <v>61</v>
-      </c>
-      <c r="B4" s="37"/>
-      <c r="C4" s="37"/>
-      <c r="D4" s="37"/>
+      <c r="A4" s="30" t="s">
+        <v>56</v>
+      </c>
+      <c r="B4" s="35"/>
+      <c r="C4" s="35"/>
+      <c r="D4" s="35"/>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="6"/>
@@ -1888,7 +1904,7 @@
       <c r="A9" s="24" t="s">
         <v>42</v>
       </c>
-      <c r="B9" s="29" t="s">
+      <c r="B9" s="28" t="s">
         <v>47</v>
       </c>
     </row>
@@ -1897,7 +1913,7 @@
         <v>49</v>
       </c>
       <c r="B10" s="27" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C10" s="27" t="s">
         <v>48</v>
@@ -1937,13 +1953,24 @@
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A14" s="12" t="s">
+      <c r="A14" s="36" t="s">
+        <v>33</v>
+      </c>
+      <c r="B14" s="27">
+        <v>0</v>
+      </c>
+      <c r="C14" s="27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="B14" s="27">
-        <v>0</v>
-      </c>
-      <c r="C14" s="27">
+      <c r="B15" s="27">
+        <v>0</v>
+      </c>
+      <c r="C15" s="27">
         <v>0</v>
       </c>
     </row>

--- a/ebegu-server/src/main/resources/reporting/Zahlungen_DE.xlsx
+++ b/ebegu-server/src/main/resources/reporting/Zahlungen_DE.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aese\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projekte\kibon-app\ebegu-server\src\main\resources\reporting\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C0C6879-299A-42DA-9571-DA89C0497D1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69AA0A07-A264-471E-826E-3BB9F7FA3D12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="-16320" windowWidth="29040" windowHeight="15720" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="0" r:id="rId4"/>
+    <pivotCache cacheId="25" r:id="rId4"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="65">
   <si>
     <t>Zahlungen</t>
   </si>
@@ -267,6 +267,9 @@
   </si>
   <si>
     <t>Jahr</t>
+  </si>
+  <si>
+    <t>#WERT!</t>
   </si>
 </sst>
 </file>
@@ -404,7 +407,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyBorder="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -478,6 +481,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" indent="3"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="9">
     <cellStyle name="Neutral 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000006000000}"/>
@@ -490,7 +496,61 @@
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
     <cellStyle name="Standard 2" xfId="8" xr:uid="{00000000-0005-0000-0000-00000D000000}"/>
   </cellStyles>
-  <dxfs count="20">
+  <dxfs count="38">
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1" indent="0"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1" indent="0"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1" indent="0"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1" indent="0"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1" indent="0"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1" indent="0"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FFFF0000"/>
@@ -637,7 +697,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Aeschlimann Severin" refreshedDate="45988.463295370369" createdVersion="3" refreshedVersion="8" recordCount="2" xr:uid="{00000000-000A-0000-FFFF-FFFF01000000}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Kafader Simon" refreshedDate="46027.431258912038" createdVersion="3" refreshedVersion="8" recordCount="2" xr:uid="{00000000-000A-0000-FFFF-FFFF01000000}">
   <cacheSource type="worksheet">
     <worksheetSource ref="A12:V1048576" sheet="Data"/>
   </cacheSource>
@@ -691,9 +751,10 @@
       </sharedItems>
     </cacheField>
     <cacheField name="Jahr" numFmtId="0">
-      <sharedItems containsBlank="1" count="2">
-        <s v="{zeitabschnittVon}"/>
+      <sharedItems containsBlank="1" count="3">
+        <e v="#VALUE!"/>
         <m/>
+        <s v="{zeitabschnittVon}" u="1"/>
       </sharedItems>
     </cacheField>
     <cacheField name="bis" numFmtId="14">
@@ -800,7 +861,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0100-000000000000}" name="PivotTable1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0" dataCaption="Values" grandTotalCaption="Verfügte Betreuungsgutscheine" updatedVersion="8" itemPrintTitles="1" indent="0" outline="1" outlineData="1" rowHeaderCaption="Filter">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0100-000000000000}" name="PivotTable1" cacheId="25" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0" dataCaption="Values" grandTotalCaption="Verfügte Betreuungsgutscheine" updatedVersion="8" itemPrintTitles="1" indent="0" outline="1" outlineData="1" rowHeaderCaption="Filter">
   <location ref="A8:C16" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="22">
     <pivotField showAll="0"/>
@@ -845,9 +906,10 @@
       </items>
     </pivotField>
     <pivotField axis="axisRow" showAll="0" includeNewItemsInFilter="1">
-      <items count="3">
+      <items count="4">
+        <item m="1" x="2"/>
+        <item x="1"/>
         <item x="0"/>
-        <item x="1"/>
         <item t="default"/>
       </items>
     </pivotField>
@@ -898,7 +960,7 @@
       <x/>
     </i>
     <i r="4">
-      <x/>
+      <x v="2"/>
     </i>
     <i r="5">
       <x/>
@@ -925,41 +987,41 @@
     <dataField name="Summe von Betrag in CHF" fld="14" baseField="2" baseItem="0"/>
   </dataFields>
   <formats count="12">
-    <format dxfId="19">
+    <format dxfId="37">
       <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="18">
+    <format dxfId="36">
       <pivotArea outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="17">
+    <format dxfId="35">
       <pivotArea type="origin" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="16">
+    <format dxfId="34">
       <pivotArea type="topRight" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="15">
+    <format dxfId="33">
       <pivotArea field="2" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="14">
+    <format dxfId="32">
       <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="13">
+    <format dxfId="31">
       <pivotArea outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="12">
+    <format dxfId="30">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="19" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="11">
+    <format dxfId="29">
       <pivotArea field="20" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisCol" fieldPosition="0"/>
     </format>
-    <format dxfId="10">
+    <format dxfId="28">
       <pivotArea type="topRight" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="9">
+    <format dxfId="27">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="20" count="1">
@@ -968,7 +1030,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="8">
+    <format dxfId="26">
       <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
     </format>
   </formats>
@@ -982,7 +1044,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0200-000000000000}" name="DataPilot1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0" dataCaption="Values" grandTotalCaption="Verfügte Betreuungsgutscheine" updatedVersion="8" itemPrintTitles="1" indent="0" outline="1" outlineData="1" rowHeaderCaption="Filter">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0200-000000000000}" name="DataPilot1" cacheId="25" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0" dataCaption="Values" grandTotalCaption="Verfügte Betreuungsgutscheine" updatedVersion="8" itemPrintTitles="1" indent="0" outline="1" outlineData="1" rowHeaderCaption="Filter">
   <location ref="A9:C15" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="22">
     <pivotField showAll="0"/>
@@ -1015,9 +1077,10 @@
       </items>
     </pivotField>
     <pivotField axis="axisRow" showAll="0" includeNewItemsInFilter="1">
-      <items count="3">
+      <items count="4">
+        <item m="1" x="2"/>
+        <item x="1"/>
         <item x="0"/>
-        <item x="1"/>
         <item t="default"/>
       </items>
     </pivotField>
@@ -1059,7 +1122,7 @@
       <x/>
     </i>
     <i r="2">
-      <x/>
+      <x v="2"/>
     </i>
     <i r="3">
       <x/>
@@ -1086,23 +1149,23 @@
     <dataField name="Summe von Betrag in CHF" fld="14" baseField="2" baseItem="0"/>
   </dataFields>
   <formats count="6">
-    <format dxfId="7">
+    <format dxfId="25">
       <pivotArea outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="6">
+    <format dxfId="24">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="19" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="5">
+    <format dxfId="23">
       <pivotArea field="21" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisCol" fieldPosition="0"/>
     </format>
-    <format dxfId="4">
+    <format dxfId="22">
       <pivotArea type="topRight" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="3">
+    <format dxfId="21">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="21" count="1">
@@ -1111,7 +1174,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="2">
+    <format dxfId="20">
       <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
     </format>
   </formats>
@@ -1440,8 +1503,8 @@
     <col min="16" max="16" width="11.42578125" style="4"/>
     <col min="17" max="17" width="18.85546875" style="4" customWidth="1"/>
     <col min="18" max="19" width="23.28515625" customWidth="1"/>
-    <col min="20" max="21" width="21.140625" hidden="1" customWidth="1"/>
-    <col min="22" max="22" width="23.42578125" style="4" hidden="1" customWidth="1"/>
+    <col min="20" max="21" width="21.140625" customWidth="1"/>
+    <col min="22" max="22" width="23.42578125" style="4" customWidth="1"/>
     <col min="23" max="23" width="12.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1659,12 +1722,12 @@
     <sortCondition ref="J13"/>
   </sortState>
   <conditionalFormatting sqref="A13:P13 R13:W13">
-    <cfRule type="expression" dxfId="1" priority="4">
+    <cfRule type="expression" dxfId="19" priority="4">
       <formula>$N13="X"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q13">
-    <cfRule type="expression" dxfId="0" priority="1">
+    <cfRule type="expression" dxfId="18" priority="1">
       <formula>$M13="X"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -1763,10 +1826,10 @@
       <c r="A10" s="33" t="s">
         <v>27</v>
       </c>
-      <c r="B10" s="27">
-        <v>0</v>
-      </c>
-      <c r="C10" s="27">
+      <c r="B10" s="37">
+        <v>0</v>
+      </c>
+      <c r="C10" s="37">
         <v>0</v>
       </c>
     </row>
@@ -1774,10 +1837,10 @@
       <c r="A11" s="33" t="s">
         <v>28</v>
       </c>
-      <c r="B11" s="27">
-        <v>0</v>
-      </c>
-      <c r="C11" s="27">
+      <c r="B11" s="37">
+        <v>0</v>
+      </c>
+      <c r="C11" s="37">
         <v>0</v>
       </c>
     </row>
@@ -1785,10 +1848,10 @@
       <c r="A12" s="33" t="s">
         <v>46</v>
       </c>
-      <c r="B12" s="27">
-        <v>0</v>
-      </c>
-      <c r="C12" s="27">
+      <c r="B12" s="37">
+        <v>0</v>
+      </c>
+      <c r="C12" s="37">
         <v>0</v>
       </c>
     </row>
@@ -1796,21 +1859,21 @@
       <c r="A13" s="33" t="s">
         <v>32</v>
       </c>
-      <c r="B13" s="27">
-        <v>0</v>
-      </c>
-      <c r="C13" s="27">
+      <c r="B13" s="37">
+        <v>0</v>
+      </c>
+      <c r="C13" s="37">
         <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="33" t="s">
-        <v>33</v>
-      </c>
-      <c r="B14" s="27">
-        <v>0</v>
-      </c>
-      <c r="C14" s="27">
+        <v>64</v>
+      </c>
+      <c r="B14" s="37">
+        <v>0</v>
+      </c>
+      <c r="C14" s="37">
         <v>0</v>
       </c>
     </row>
@@ -1818,10 +1881,10 @@
       <c r="A15" s="33" t="s">
         <v>33</v>
       </c>
-      <c r="B15" s="27">
-        <v>0</v>
-      </c>
-      <c r="C15" s="27">
+      <c r="B15" s="37">
+        <v>0</v>
+      </c>
+      <c r="C15" s="37">
         <v>0</v>
       </c>
     </row>
@@ -1829,10 +1892,10 @@
       <c r="A16" s="33" t="s">
         <v>48</v>
       </c>
-      <c r="B16" s="27">
-        <v>0</v>
-      </c>
-      <c r="C16" s="27">
+      <c r="B16" s="37">
+        <v>0</v>
+      </c>
+      <c r="C16" s="37">
         <v>0</v>
       </c>
     </row>
@@ -1923,10 +1986,10 @@
       <c r="A11" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="B11" s="27">
-        <v>0</v>
-      </c>
-      <c r="C11" s="27">
+      <c r="B11" s="37">
+        <v>0</v>
+      </c>
+      <c r="C11" s="37">
         <v>0</v>
       </c>
     </row>
@@ -1934,21 +1997,21 @@
       <c r="A12" s="25" t="s">
         <v>28</v>
       </c>
-      <c r="B12" s="27">
-        <v>0</v>
-      </c>
-      <c r="C12" s="27">
+      <c r="B12" s="37">
+        <v>0</v>
+      </c>
+      <c r="C12" s="37">
         <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="26" t="s">
-        <v>33</v>
-      </c>
-      <c r="B13" s="27">
-        <v>0</v>
-      </c>
-      <c r="C13" s="27">
+        <v>64</v>
+      </c>
+      <c r="B13" s="37">
+        <v>0</v>
+      </c>
+      <c r="C13" s="37">
         <v>0</v>
       </c>
     </row>
@@ -1956,10 +2019,10 @@
       <c r="A14" s="36" t="s">
         <v>33</v>
       </c>
-      <c r="B14" s="27">
-        <v>0</v>
-      </c>
-      <c r="C14" s="27">
+      <c r="B14" s="37">
+        <v>0</v>
+      </c>
+      <c r="C14" s="37">
         <v>0</v>
       </c>
     </row>
@@ -1967,10 +2030,10 @@
       <c r="A15" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="B15" s="27">
-        <v>0</v>
-      </c>
-      <c r="C15" s="27">
+      <c r="B15" s="37">
+        <v>0</v>
+      </c>
+      <c r="C15" s="37">
         <v>0</v>
       </c>
     </row>

--- a/ebegu-server/src/main/resources/reporting/Zahlungen_DE.xlsx
+++ b/ebegu-server/src/main/resources/reporting/Zahlungen_DE.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10201"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projekte\kibon-app\ebegu-server\src\main\resources\reporting\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/frederic.nell/IdeaProjects/kibon-app/ebegu-server/src/main/resources/reporting/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69AA0A07-A264-471E-826E-3BB9F7FA3D12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F5243C3-E22B-E44A-BCE9-D1023CFCB081}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="29040" windowHeight="17520" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="25" r:id="rId4"/>
+    <pivotCache cacheId="1" r:id="rId4"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -182,13 +182,7 @@
     <t>Nachname, Vorname</t>
   </si>
   <si>
-    <t>(Mehrere Elemente)</t>
-  </si>
-  <si>
     <t>{kindNachname} {kindVorname}</t>
-  </si>
-  <si>
-    <t>Spaltenbeschriftungen</t>
   </si>
   <si>
     <t>Verfügte Betreuungsgutscheine</t>
@@ -269,7 +263,13 @@
     <t>Jahr</t>
   </si>
   <si>
-    <t>#WERT!</t>
+    <t>Étiquettes de colonnes</t>
+  </si>
+  <si>
+    <t>#VALEUR!</t>
+  </si>
+  <si>
+    <t>(Plusieurs éléments)</t>
   </si>
 </sst>
 </file>
@@ -487,16 +487,52 @@
   </cellXfs>
   <cellStyles count="9">
     <cellStyle name="Neutral 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000006000000}"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Pivot Table Category" xfId="2" xr:uid="{00000000-0005-0000-0000-000007000000}"/>
     <cellStyle name="Pivot Table Corner" xfId="3" xr:uid="{00000000-0005-0000-0000-000008000000}"/>
     <cellStyle name="Pivot Table Field" xfId="4" xr:uid="{00000000-0005-0000-0000-000009000000}"/>
     <cellStyle name="Pivot Table Result" xfId="5" xr:uid="{00000000-0005-0000-0000-00000A000000}"/>
     <cellStyle name="Pivot Table Title" xfId="6" xr:uid="{00000000-0005-0000-0000-00000B000000}"/>
     <cellStyle name="Pivot Table Value" xfId="7" xr:uid="{00000000-0005-0000-0000-00000C000000}"/>
-    <cellStyle name="Standard" xfId="0" builtinId="0"/>
     <cellStyle name="Standard 2" xfId="8" xr:uid="{00000000-0005-0000-0000-00000D000000}"/>
   </cellStyles>
-  <dxfs count="38">
+  <dxfs count="50">
+    <dxf>
+      <alignment wrapText="1" indent="0"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1" indent="0"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1" indent="0"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1" indent="0"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1" indent="0"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1" indent="0"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
     <dxf>
       <alignment wrapText="1"/>
     </dxf>
@@ -697,7 +733,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Kafader Simon" refreshedDate="46027.431258912038" createdVersion="3" refreshedVersion="8" recordCount="2" xr:uid="{00000000-000A-0000-FFFF-FFFF01000000}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshOnLoad="1" refreshedBy="Kafader Simon" refreshedDate="46027.431258912038" createdVersion="3" refreshedVersion="8" recordCount="2" xr:uid="{00000000-000A-0000-FFFF-FFFF01000000}">
   <cacheSource type="worksheet">
     <worksheetSource ref="A12:V1048576" sheet="Data"/>
   </cacheSource>
@@ -861,7 +897,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0100-000000000000}" name="PivotTable1" cacheId="25" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0" dataCaption="Values" grandTotalCaption="Verfügte Betreuungsgutscheine" updatedVersion="8" itemPrintTitles="1" indent="0" outline="1" outlineData="1" rowHeaderCaption="Filter">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0100-000000000000}" name="PivotTable1" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0" dataCaption="Values" grandTotalCaption="Verfügte Betreuungsgutscheine" updatedVersion="8" itemPrintTitles="1" indent="0" outline="1" outlineData="1" rowHeaderCaption="Filter">
   <location ref="A8:C16" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="22">
     <pivotField showAll="0"/>
@@ -987,41 +1023,41 @@
     <dataField name="Summe von Betrag in CHF" fld="14" baseField="2" baseItem="0"/>
   </dataFields>
   <formats count="12">
-    <format dxfId="37">
+    <format dxfId="49">
       <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="36">
+    <format dxfId="48">
       <pivotArea outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="35">
+    <format dxfId="47">
       <pivotArea type="origin" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="34">
+    <format dxfId="46">
       <pivotArea type="topRight" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="33">
+    <format dxfId="45">
       <pivotArea field="2" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="32">
+    <format dxfId="44">
       <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="31">
+    <format dxfId="43">
       <pivotArea outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="30">
+    <format dxfId="42">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="19" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="29">
+    <format dxfId="41">
       <pivotArea field="20" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisCol" fieldPosition="0"/>
     </format>
-    <format dxfId="28">
+    <format dxfId="40">
       <pivotArea type="topRight" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="27">
+    <format dxfId="39">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="20" count="1">
@@ -1030,7 +1066,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="26">
+    <format dxfId="38">
       <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
     </format>
   </formats>
@@ -1044,7 +1080,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0200-000000000000}" name="DataPilot1" cacheId="25" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0" dataCaption="Values" grandTotalCaption="Verfügte Betreuungsgutscheine" updatedVersion="8" itemPrintTitles="1" indent="0" outline="1" outlineData="1" rowHeaderCaption="Filter">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0200-000000000000}" name="DataPilot1" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0" dataCaption="Values" grandTotalCaption="Verfügte Betreuungsgutscheine" updatedVersion="8" itemPrintTitles="1" indent="0" outline="1" outlineData="1" rowHeaderCaption="Filter">
   <location ref="A9:C15" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="22">
     <pivotField showAll="0"/>
@@ -1149,23 +1185,23 @@
     <dataField name="Summe von Betrag in CHF" fld="14" baseField="2" baseItem="0"/>
   </dataFields>
   <formats count="6">
-    <format dxfId="25">
+    <format dxfId="37">
       <pivotArea outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="24">
+    <format dxfId="36">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="19" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="23">
+    <format dxfId="35">
       <pivotArea field="21" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisCol" fieldPosition="0"/>
     </format>
-    <format dxfId="22">
+    <format dxfId="34">
       <pivotArea type="topRight" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="21">
+    <format dxfId="33">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="21" count="1">
@@ -1174,7 +1210,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="20">
+    <format dxfId="32">
       <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
     </format>
   </formats>
@@ -1188,9 +1224,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 – 2022-Design">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Thème Office 2013 – 2022">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 – 2022">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1228,7 +1264,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 – 2022">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -1334,7 +1370,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 – 2022">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1485,36 +1521,36 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:W13"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="21.140625" customWidth="1"/>
-    <col min="2" max="2" width="21.140625" style="23" customWidth="1"/>
-    <col min="3" max="4" width="21.140625" customWidth="1"/>
-    <col min="5" max="5" width="30.85546875" style="1" customWidth="1"/>
-    <col min="6" max="7" width="30.85546875" customWidth="1"/>
-    <col min="8" max="8" width="14.140625" hidden="1" customWidth="1"/>
-    <col min="9" max="9" width="21.140625" customWidth="1"/>
-    <col min="10" max="10" width="19.42578125" style="23" customWidth="1"/>
-    <col min="11" max="11" width="11.140625" style="23" hidden="1" customWidth="1"/>
-    <col min="12" max="12" width="13.7109375" style="23" hidden="1" customWidth="1"/>
-    <col min="13" max="13" width="19.42578125" style="23" customWidth="1"/>
-    <col min="14" max="14" width="19.42578125" style="2" customWidth="1"/>
-    <col min="15" max="15" width="16.42578125" style="3" customWidth="1"/>
-    <col min="16" max="16" width="11.42578125" style="4"/>
-    <col min="17" max="17" width="18.85546875" style="4" customWidth="1"/>
-    <col min="18" max="19" width="23.28515625" customWidth="1"/>
-    <col min="20" max="21" width="21.140625" customWidth="1"/>
-    <col min="22" max="22" width="23.42578125" style="4" customWidth="1"/>
-    <col min="23" max="23" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="21.1640625" customWidth="1"/>
+    <col min="2" max="2" width="21.1640625" style="23" customWidth="1"/>
+    <col min="3" max="4" width="21.1640625" customWidth="1"/>
+    <col min="5" max="5" width="30.83203125" style="1" customWidth="1"/>
+    <col min="6" max="7" width="30.83203125" customWidth="1"/>
+    <col min="8" max="8" width="14.1640625" hidden="1" customWidth="1"/>
+    <col min="9" max="9" width="21.1640625" customWidth="1"/>
+    <col min="10" max="10" width="19.5" style="23" customWidth="1"/>
+    <col min="11" max="11" width="11.1640625" style="23" hidden="1" customWidth="1"/>
+    <col min="12" max="12" width="13.6640625" style="23" hidden="1" customWidth="1"/>
+    <col min="13" max="13" width="19.5" style="23" customWidth="1"/>
+    <col min="14" max="14" width="19.5" style="2" customWidth="1"/>
+    <col min="15" max="15" width="16.5" style="3" customWidth="1"/>
+    <col min="16" max="16" width="11.5" style="4"/>
+    <col min="17" max="17" width="18.83203125" style="4" customWidth="1"/>
+    <col min="18" max="19" width="23.33203125" customWidth="1"/>
+    <col min="20" max="21" width="21.1640625" customWidth="1"/>
+    <col min="22" max="22" width="23.5" style="4" customWidth="1"/>
+    <col min="23" max="23" width="12.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" ht="21" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:23" ht="21" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="18"/>
     </row>
-    <row r="3" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A3" s="6" t="s">
         <v>1</v>
       </c>
@@ -1522,7 +1558,7 @@
       <c r="T3" s="6"/>
       <c r="U3" s="6"/>
     </row>
-    <row r="4" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>2</v>
       </c>
@@ -1530,7 +1566,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -1538,7 +1574,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -1546,7 +1582,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -1554,23 +1590,23 @@
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
+        <v>56</v>
+      </c>
+      <c r="B8" s="20" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>57</v>
+      </c>
+      <c r="B9" s="20" t="s">
         <v>58</v>
       </c>
-      <c r="B8" s="20" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="9" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>59</v>
-      </c>
-      <c r="B9" s="20" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="12" spans="1:23" s="12" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    </row>
+    <row r="12" spans="1:23" s="12" customFormat="1" ht="32" x14ac:dyDescent="0.2">
       <c r="A12" s="7" t="s">
         <v>10</v>
       </c>
@@ -1602,10 +1638,10 @@
         <v>16</v>
       </c>
       <c r="K12" s="21" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="L12" s="21" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="M12" s="21" t="s">
         <v>17</v>
@@ -1632,13 +1668,13 @@
         <v>24</v>
       </c>
       <c r="U12" s="7" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="V12" s="7" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="13" spans="1:23" x14ac:dyDescent="0.25">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A13" s="13" t="s">
         <v>25</v>
       </c>
@@ -1722,12 +1758,12 @@
     <sortCondition ref="J13"/>
   </sortState>
   <conditionalFormatting sqref="A13:P13 R13:W13">
-    <cfRule type="expression" dxfId="19" priority="4">
+    <cfRule type="expression" dxfId="31" priority="4">
       <formula>$N13="X"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q13">
-    <cfRule type="expression" dxfId="18" priority="1">
+    <cfRule type="expression" dxfId="30" priority="1">
       <formula>$M13="X"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -1739,63 +1775,63 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:E16"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="26.85546875" style="27" customWidth="1"/>
-    <col min="2" max="2" width="22.28515625" style="27" customWidth="1"/>
-    <col min="3" max="3" width="26.85546875" style="27" customWidth="1"/>
-    <col min="4" max="4" width="24.28515625" style="27" customWidth="1"/>
-    <col min="5" max="5" width="13.42578125" style="27" customWidth="1"/>
-    <col min="6" max="6" width="16.85546875" style="27" customWidth="1"/>
-    <col min="7" max="7" width="13.28515625" style="27" customWidth="1"/>
-    <col min="8" max="8" width="25.7109375" style="27" customWidth="1"/>
-    <col min="9" max="16384" width="11.42578125" style="27"/>
+    <col min="1" max="1" width="26.83203125" style="27" customWidth="1"/>
+    <col min="2" max="2" width="22.33203125" style="27" customWidth="1"/>
+    <col min="3" max="3" width="26.83203125" style="27" customWidth="1"/>
+    <col min="4" max="4" width="24.33203125" style="27" customWidth="1"/>
+    <col min="5" max="5" width="13.5" style="27" customWidth="1"/>
+    <col min="6" max="6" width="16.83203125" style="27" customWidth="1"/>
+    <col min="7" max="7" width="13.33203125" style="27" customWidth="1"/>
+    <col min="8" max="8" width="25.6640625" style="27" customWidth="1"/>
+    <col min="9" max="16384" width="11.5" style="27"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" customFormat="1" ht="21" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5" customFormat="1" ht="21" x14ac:dyDescent="0.25">
       <c r="A1" s="29" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B1" s="31"/>
       <c r="C1" s="31"/>
       <c r="D1" s="31"/>
       <c r="E1" s="34"/>
     </row>
-    <row r="2" spans="1:5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A2" s="30" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B2" s="31"/>
       <c r="C2" s="31"/>
       <c r="D2" s="31"/>
       <c r="E2" s="34"/>
     </row>
-    <row r="3" spans="1:5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A3" s="30" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B3" s="31"/>
       <c r="C3" s="31"/>
       <c r="D3" s="31"/>
       <c r="E3" s="34"/>
     </row>
-    <row r="4" spans="1:5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A4" s="30" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B4" s="31"/>
       <c r="C4" s="31"/>
       <c r="D4" s="31"/>
       <c r="E4" s="34"/>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5" s="32"/>
       <c r="B5" s="31"/>
       <c r="C5" s="31"/>
       <c r="D5" s="31"/>
       <c r="E5" s="31"/>
     </row>
-    <row r="6" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A6" s="28" t="s">
         <v>24</v>
       </c>
@@ -1803,26 +1839,26 @@
         <v>43</v>
       </c>
     </row>
-    <row r="8" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A8" s="28" t="s">
         <v>42</v>
       </c>
       <c r="B8" s="28" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="49.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="28" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="9" spans="1:5" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="28" t="s">
-        <v>49</v>
-      </c>
       <c r="B9" s="27" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C9" s="27" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A10" s="33" t="s">
         <v>27</v>
       </c>
@@ -1833,7 +1869,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A11" s="33" t="s">
         <v>28</v>
       </c>
@@ -1844,9 +1880,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:5" ht="32" x14ac:dyDescent="0.2">
       <c r="A12" s="33" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B12" s="37">
         <v>0</v>
@@ -1855,7 +1891,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A13" s="33" t="s">
         <v>32</v>
       </c>
@@ -1866,9 +1902,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A14" s="33" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B14" s="37">
         <v>0</v>
@@ -1877,7 +1913,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A15" s="33" t="s">
         <v>33</v>
       </c>
@@ -1888,9 +1924,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A16" s="33" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B16" s="37">
         <v>0</v>
@@ -1908,81 +1944,81 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:D15"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="21" customWidth="1"/>
-    <col min="2" max="4" width="22.85546875" style="27" customWidth="1"/>
-    <col min="5" max="5" width="13.42578125" customWidth="1"/>
-    <col min="6" max="6" width="16.85546875" customWidth="1"/>
-    <col min="7" max="7" width="13.28515625" customWidth="1"/>
-    <col min="8" max="8" width="25.7109375" customWidth="1"/>
+    <col min="2" max="4" width="22.83203125" style="27" customWidth="1"/>
+    <col min="5" max="5" width="13.5" customWidth="1"/>
+    <col min="6" max="6" width="16.83203125" customWidth="1"/>
+    <col min="7" max="7" width="13.33203125" customWidth="1"/>
+    <col min="8" max="8" width="25.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="21" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4" ht="21" x14ac:dyDescent="0.25">
       <c r="A1" s="29" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B1" s="35"/>
       <c r="C1" s="35"/>
       <c r="D1" s="35"/>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A2" s="30" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B2" s="35"/>
       <c r="C2" s="35"/>
       <c r="D2" s="35"/>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A3" s="30" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B3" s="35"/>
       <c r="C3" s="35"/>
       <c r="D3" s="35"/>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A4" s="30" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B4" s="35"/>
       <c r="C4" s="35"/>
       <c r="D4" s="35"/>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A5" s="6"/>
     </row>
-    <row r="6" spans="1:4" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="7" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" hidden="1" x14ac:dyDescent="0.2"/>
+    <row r="7" spans="1:4" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A7" s="24" t="s">
         <v>24</v>
       </c>
       <c r="B7" s="27" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="9" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" hidden="1" x14ac:dyDescent="0.2"/>
+    <row r="9" spans="1:4" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A9" s="24" t="s">
         <v>42</v>
       </c>
       <c r="B9" s="28" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="51.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="24" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="10" spans="1:4" ht="51.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="24" t="s">
-        <v>49</v>
-      </c>
       <c r="B10" s="27" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C10" s="27" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A11" s="12" t="s">
         <v>27</v>
       </c>
@@ -1993,7 +2029,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A12" s="25" t="s">
         <v>28</v>
       </c>
@@ -2004,9 +2040,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A13" s="26" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B13" s="37">
         <v>0</v>
@@ -2015,7 +2051,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A14" s="36" t="s">
         <v>33</v>
       </c>
@@ -2026,9 +2062,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A15" s="12" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B15" s="37">
         <v>0</v>

--- a/ebegu-server/src/main/resources/reporting/Zahlungen_DE.xlsx
+++ b/ebegu-server/src/main/resources/reporting/Zahlungen_DE.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10201"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10308"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/frederic.nell/IdeaProjects/kibon-app/ebegu-server/src/main/resources/reporting/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F5243C3-E22B-E44A-BCE9-D1023CFCB081}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BABB71A0-C78B-8C4D-8695-799D8E1DAE97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="29040" windowHeight="17520" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="19980" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="1" r:id="rId4"/>
+    <pivotCache cacheId="60" r:id="rId4"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -45,14 +45,11 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="64">
   <si>
     <t>Zahlungen</t>
   </si>
   <si>
-    <t>Parameter</t>
-  </si>
-  <si>
     <t>Periode</t>
   </si>
   <si>
@@ -195,9 +192,6 @@
   </si>
   <si>
     <t>Übersicht Auszahlungen: nach Kind</t>
-  </si>
-  <si>
-    <t>Auszahlung an Institution</t>
   </si>
   <si>
     <t>Auszahlung an (für Gemeinde Pivot)</t>
@@ -271,14 +265,17 @@
   <si>
     <t>(Plusieurs éléments)</t>
   </si>
+  <si>
+    <t>Abrechnung direkt zwischen Gemeinde &amp; Antragstellenden</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="m/d/yyyy\ h:mm"/>
-    <numFmt numFmtId="165" formatCode="&quot;CHF &quot;#,##0.00"/>
+    <numFmt numFmtId="164" formatCode="&quot;CHF &quot;#,##0.00"/>
+    <numFmt numFmtId="165" formatCode="&quot;CHF&quot;\ #,##0.00"/>
   </numFmts>
   <fonts count="9" x14ac:knownFonts="1">
     <font>
@@ -409,9 +406,9 @@
   </cellStyleXfs>
   <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -420,13 +417,13 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="22" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="10" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -436,15 +433,14 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="22" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="14" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="14" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -481,8 +477,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" indent="3"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="9">
@@ -496,96 +495,84 @@
     <cellStyle name="Pivot Table Value" xfId="7" xr:uid="{00000000-0005-0000-0000-00000C000000}"/>
     <cellStyle name="Standard 2" xfId="8" xr:uid="{00000000-0005-0000-0000-00000D000000}"/>
   </cellStyles>
-  <dxfs count="50">
-    <dxf>
-      <alignment wrapText="1" indent="0"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1" indent="0"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1" indent="0"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1" indent="0"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1" indent="0"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1" indent="0"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1" indent="0"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1" indent="0"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1" indent="0"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1" indent="0"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1" indent="0"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1" indent="0"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
+  <dxfs count="119">
+    <dxf>
+      <numFmt numFmtId="165" formatCode="&quot;CHF&quot;\ #,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="&quot;CHF&quot;\ #,##0.00"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="&quot;CHF&quot;\ #,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="&quot;CHF&quot;\ #,##0.00"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1" indent="0"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1" indent="0"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1" indent="0"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1" indent="0"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1" indent="0"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1" indent="0"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="&quot;CHF&quot;\ #,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="&quot;CHF&quot;\ #,##0.00"/>
     </dxf>
     <dxf>
       <font>
@@ -622,34 +609,253 @@
       <alignment wrapText="1"/>
     </dxf>
     <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1" indent="0"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1" indent="0"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1" indent="0"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1" indent="0"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1" indent="0"/>
-    </dxf>
-    <dxf>
-      <alignment wrapText="1" indent="0"/>
+      <numFmt numFmtId="165" formatCode="&quot;CHF&quot;\ #,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="&quot;CHF&quot;\ #,##0.00"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1" indent="0"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1" indent="0"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1" indent="0"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1" indent="0"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1" indent="0"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1" indent="0"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="&quot;CHF&quot;\ #,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="&quot;CHF&quot;\ #,##0.00"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="&quot;CHF&quot;\ #,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="&quot;CHF&quot;\ #,##0.00"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1" indent="0"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1" indent="0"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1" indent="0"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1" indent="0"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1" indent="0"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1" indent="0"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="&quot;CHF&quot;\ #,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="&quot;CHF&quot;\ #,##0.00"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="&quot;CHF&quot;\ #,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="&quot;CHF&quot;\ #,##0.00"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1" indent="0"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1" indent="0"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1" indent="0"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1" indent="0"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1" indent="0"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1" indent="0"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="&quot;CHF&quot;\ #,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="&quot;CHF&quot;\ #,##0.00"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1" indent="0"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1" indent="0"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1" indent="0"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1" indent="0"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1" indent="0"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1" indent="0"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -733,7 +939,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshOnLoad="1" refreshedBy="Kafader Simon" refreshedDate="46027.431258912038" createdVersion="3" refreshedVersion="8" recordCount="2" xr:uid="{00000000-000A-0000-FFFF-FFFF01000000}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshOnLoad="1" refreshedBy="Nell Frédéric" refreshedDate="46092.519869212963" createdVersion="3" refreshedVersion="8" recordCount="4" xr:uid="{00000000-000A-0000-FFFF-FFFF01000000}">
   <cacheSource type="worksheet">
     <worksheetSource ref="A12:V1048576" sheet="Data"/>
   </cacheSource>
@@ -756,7 +962,7 @@
         <m/>
       </sharedItems>
     </cacheField>
-    <cacheField name="Erstellungsdatum Zahlungslauf" numFmtId="164">
+    <cacheField name="Erstellungsdatum Zahlungslauf" numFmtId="22">
       <sharedItems containsBlank="1"/>
     </cacheField>
     <cacheField name="Kind Nachname" numFmtId="0">
@@ -799,7 +1005,7 @@
     <cacheField name="BG-Pensum" numFmtId="10">
       <sharedItems containsBlank="1"/>
     </cacheField>
-    <cacheField name="Betrag in CHF" numFmtId="165">
+    <cacheField name="Betrag in CHF" numFmtId="164">
       <sharedItems containsBlank="1"/>
     </cacheField>
     <cacheField name="Korrektur" numFmtId="0">
@@ -822,16 +1028,18 @@
       </sharedItems>
     </cacheField>
     <cacheField name="Auszahlung an (für Kind Pivot)" numFmtId="0">
-      <sharedItems containsBlank="1" count="3">
-        <s v="Auszahlung an Institution"/>
+      <sharedItems containsBlank="1" count="4">
+        <s v="Abrechnung direkt zwischen Gemeinde &amp; Antragstellenden"/>
         <m/>
+        <s v="Auszahlung an Institution" u="1"/>
         <e v="#REF!" u="1"/>
       </sharedItems>
     </cacheField>
     <cacheField name="Auszahlung an (für Gemeinde Pivot)" numFmtId="0">
-      <sharedItems containsBlank="1" count="2">
-        <s v="Auszahlung an Institution"/>
+      <sharedItems containsBlank="1" count="3">
+        <s v="Abrechnung direkt zwischen Gemeinde &amp; Antragstellenden"/>
         <m/>
+        <s v="Auszahlung an Institution" u="1"/>
       </sharedItems>
     </cacheField>
   </cacheFields>
@@ -844,7 +1052,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheRecords1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="2">
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="4">
   <r>
     <s v="{zahlungslaufTitle}"/>
     <s v="{faelligkeitsDatum}"/>
@@ -862,7 +1070,7 @@
     <s v="{bgPensum}"/>
     <s v="{betrag}"/>
     <s v="{korrektur}"/>
-    <s v="{ignorieren}"/>
+    <s v="x"/>
     <s v="{ibanEltern}"/>
     <s v="{kontoEltern}"/>
     <x v="0"/>
@@ -893,11 +1101,59 @@
     <x v="1"/>
     <x v="1"/>
   </r>
+  <r>
+    <m/>
+    <m/>
+    <x v="1"/>
+    <x v="1"/>
+    <m/>
+    <m/>
+    <m/>
+    <x v="1"/>
+    <x v="1"/>
+    <m/>
+    <x v="1"/>
+    <x v="1"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <x v="1"/>
+    <x v="1"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <m/>
+    <m/>
+    <x v="1"/>
+    <x v="1"/>
+    <m/>
+    <m/>
+    <m/>
+    <x v="1"/>
+    <x v="1"/>
+    <m/>
+    <x v="1"/>
+    <x v="1"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <x v="1"/>
+    <x v="1"/>
+    <x v="1"/>
+  </r>
 </pivotCacheRecords>
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0100-000000000000}" name="PivotTable1" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0" dataCaption="Values" grandTotalCaption="Verfügte Betreuungsgutscheine" updatedVersion="8" itemPrintTitles="1" indent="0" outline="1" outlineData="1" rowHeaderCaption="Filter">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0100-000000000000}" name="PivotTable1" cacheId="60" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0" dataCaption="Values" grandTotalCaption="Verfügte Betreuungsgutscheine" updatedVersion="8" itemPrintTitles="1" indent="0" outline="1" outlineData="1" rowHeaderCaption="Filter">
   <location ref="A8:C16" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="22">
     <pivotField showAll="0"/>
@@ -965,9 +1221,10 @@
       </items>
     </pivotField>
     <pivotField axis="axisCol" showAll="0" includeNewItemsInFilter="1">
-      <items count="4">
+      <items count="5">
+        <item m="1" x="3"/>
+        <item x="1"/>
         <item m="1" x="2"/>
-        <item x="1"/>
         <item x="0"/>
         <item t="default"/>
       </items>
@@ -1010,7 +1267,7 @@
   </colFields>
   <colItems count="2">
     <i>
-      <x v="2"/>
+      <x v="3"/>
     </i>
     <i t="grand">
       <x/>
@@ -1022,42 +1279,42 @@
   <dataFields count="1">
     <dataField name="Summe von Betrag in CHF" fld="14" baseField="2" baseItem="0"/>
   </dataFields>
-  <formats count="12">
-    <format dxfId="49">
+  <formats count="15">
+    <format dxfId="38">
       <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="48">
+    <format dxfId="39">
       <pivotArea outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="47">
+    <format dxfId="40">
       <pivotArea type="origin" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="46">
+    <format dxfId="41">
       <pivotArea type="topRight" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
+    <format dxfId="42">
+      <pivotArea field="2" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
+    </format>
+    <format dxfId="43">
+      <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="44">
+      <pivotArea outline="0" fieldPosition="0"/>
+    </format>
     <format dxfId="45">
-      <pivotArea field="2" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
-    </format>
-    <format dxfId="44">
-      <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="43">
-      <pivotArea outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="42">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="19" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="41">
+    <format dxfId="46">
       <pivotArea field="20" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisCol" fieldPosition="0"/>
     </format>
-    <format dxfId="40">
+    <format dxfId="47">
       <pivotArea type="topRight" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="39">
+    <format dxfId="48">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="20" count="1">
@@ -1066,8 +1323,29 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="38">
+    <format dxfId="49">
       <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="50">
+      <pivotArea outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="20" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="51">
+      <pivotArea grandCol="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="1">
+      <pivotArea outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="20" count="1" selected="0">
+            <x v="3"/>
+          </reference>
+        </references>
+      </pivotArea>
     </format>
   </formats>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
@@ -1080,7 +1358,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0200-000000000000}" name="DataPilot1" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0" dataCaption="Values" grandTotalCaption="Verfügte Betreuungsgutscheine" updatedVersion="8" itemPrintTitles="1" indent="0" outline="1" outlineData="1" rowHeaderCaption="Filter">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0200-000000000000}" name="DataPilot1" cacheId="60" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0" dataCaption="Values" grandTotalCaption="Verfügte Betreuungsgutscheine" updatedVersion="8" itemPrintTitles="1" indent="0" outline="1" outlineData="1" rowHeaderCaption="Filter">
   <location ref="A9:C15" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="22">
     <pivotField showAll="0"/>
@@ -1137,9 +1415,10 @@
     </pivotField>
     <pivotField showAll="0" includeNewItemsInFilter="1"/>
     <pivotField axis="axisCol" showAll="0" includeNewItemsInFilter="1">
-      <items count="3">
+      <items count="4">
+        <item m="1" x="2"/>
+        <item x="1"/>
         <item x="0"/>
-        <item x="1"/>
         <item t="default"/>
       </items>
     </pivotField>
@@ -1172,7 +1451,7 @@
   </colFields>
   <colItems count="2">
     <i>
-      <x/>
+      <x v="2"/>
     </i>
     <i t="grand">
       <x/>
@@ -1184,24 +1463,24 @@
   <dataFields count="1">
     <dataField name="Summe von Betrag in CHF" fld="14" baseField="2" baseItem="0"/>
   </dataFields>
-  <formats count="6">
-    <format dxfId="37">
+  <formats count="11">
+    <format dxfId="28">
       <pivotArea outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="36">
+    <format dxfId="29">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="19" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="35">
+    <format dxfId="30">
       <pivotArea field="21" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisCol" fieldPosition="0"/>
     </format>
-    <format dxfId="34">
+    <format dxfId="31">
       <pivotArea type="topRight" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="33">
+    <format dxfId="32">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="21" count="1">
@@ -1210,8 +1489,41 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="32">
+    <format dxfId="33">
       <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="34">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="1">
+          <reference field="21" count="1">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="35">
+      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="36">
+      <pivotArea outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="21" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="37">
+      <pivotArea grandCol="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="0">
+      <pivotArea outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="21" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
     </format>
   </formats>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
@@ -1524,23 +1836,24 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="21.1640625" customWidth="1"/>
-    <col min="2" max="2" width="21.1640625" style="23" customWidth="1"/>
+    <col min="2" max="2" width="21.1640625" style="22" customWidth="1"/>
     <col min="3" max="4" width="21.1640625" customWidth="1"/>
     <col min="5" max="5" width="30.83203125" style="1" customWidth="1"/>
     <col min="6" max="7" width="30.83203125" customWidth="1"/>
     <col min="8" max="8" width="14.1640625" hidden="1" customWidth="1"/>
     <col min="9" max="9" width="21.1640625" customWidth="1"/>
-    <col min="10" max="10" width="19.5" style="23" customWidth="1"/>
-    <col min="11" max="11" width="11.1640625" style="23" hidden="1" customWidth="1"/>
-    <col min="12" max="12" width="13.6640625" style="23" hidden="1" customWidth="1"/>
-    <col min="13" max="13" width="19.5" style="23" customWidth="1"/>
+    <col min="10" max="10" width="19.5" style="22" customWidth="1"/>
+    <col min="11" max="11" width="11.1640625" style="22" hidden="1" customWidth="1"/>
+    <col min="12" max="12" width="13.6640625" style="22" hidden="1" customWidth="1"/>
+    <col min="13" max="13" width="19.5" style="22" customWidth="1"/>
     <col min="14" max="14" width="19.5" style="2" customWidth="1"/>
     <col min="15" max="15" width="16.5" style="3" customWidth="1"/>
     <col min="16" max="16" width="11.5" style="4"/>
     <col min="17" max="17" width="18.83203125" style="4" customWidth="1"/>
-    <col min="18" max="19" width="23.33203125" customWidth="1"/>
-    <col min="20" max="21" width="21.1640625" customWidth="1"/>
-    <col min="22" max="22" width="23.5" style="4" customWidth="1"/>
+    <col min="18" max="18" width="23.33203125" customWidth="1"/>
+    <col min="19" max="19" width="19.33203125" customWidth="1"/>
+    <col min="20" max="21" width="21.1640625" hidden="1" customWidth="1"/>
+    <col min="22" max="22" width="23.5" style="4" hidden="1" customWidth="1"/>
     <col min="23" max="23" width="12.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1551,162 +1864,160 @@
       <c r="B1" s="18"/>
     </row>
     <row r="3" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A3" s="6" t="s">
-        <v>1</v>
-      </c>
+      <c r="A3" s="6"/>
       <c r="B3" s="19"/>
       <c r="T3" s="6"/>
       <c r="U3" s="6"/>
     </row>
     <row r="4" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4" s="37" t="s">
         <v>2</v>
-      </c>
-      <c r="B4" s="20" t="s">
-        <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" s="37" t="s">
         <v>4</v>
-      </c>
-      <c r="B5" s="20" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6" s="37" t="s">
         <v>6</v>
-      </c>
-      <c r="B6" s="20" t="s">
-        <v>7</v>
       </c>
     </row>
     <row r="7" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7" s="37" t="s">
         <v>8</v>
-      </c>
-      <c r="B7" s="20" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="8" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>56</v>
-      </c>
-      <c r="B8" s="20" t="s">
-        <v>59</v>
+        <v>54</v>
+      </c>
+      <c r="B8" s="37" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="9" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>57</v>
-      </c>
-      <c r="B9" s="20" t="s">
-        <v>58</v>
+        <v>55</v>
+      </c>
+      <c r="B9" s="37" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="12" spans="1:23" s="12" customFormat="1" ht="32" x14ac:dyDescent="0.2">
       <c r="A12" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="B12" s="20" t="s">
         <v>10</v>
       </c>
-      <c r="B12" s="21" t="s">
+      <c r="C12" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="E12" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="C12" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="D12" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="E12" s="8" t="s">
+      <c r="F12" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="F12" s="7" t="s">
+      <c r="G12" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="G12" s="7" t="s">
+      <c r="H12" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="I12" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="H12" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="I12" s="7" t="s">
+      <c r="J12" s="20" t="s">
         <v>15</v>
       </c>
-      <c r="J12" s="21" t="s">
+      <c r="K12" s="20" t="s">
+        <v>58</v>
+      </c>
+      <c r="L12" s="20" t="s">
+        <v>59</v>
+      </c>
+      <c r="M12" s="20" t="s">
         <v>16</v>
       </c>
-      <c r="K12" s="21" t="s">
-        <v>60</v>
-      </c>
-      <c r="L12" s="21" t="s">
-        <v>61</v>
-      </c>
-      <c r="M12" s="21" t="s">
+      <c r="N12" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="N12" s="9" t="s">
+      <c r="O12" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="O12" s="10" t="s">
+      <c r="P12" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="P12" s="7" t="s">
+      <c r="Q12" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="Q12" s="11" t="s">
+      <c r="R12" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="R12" s="11" t="s">
+      <c r="S12" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="S12" s="11" t="s">
+      <c r="T12" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="T12" s="7" t="s">
-        <v>24</v>
-      </c>
       <c r="U12" s="7" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="V12" s="7" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="13" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A13" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="B13" s="21" t="s">
         <v>25</v>
       </c>
-      <c r="B13" s="22" t="s">
+      <c r="C13" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="C13" s="13" t="s">
+      <c r="D13" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="D13" s="13" t="s">
+      <c r="E13" s="14" t="s">
         <v>28</v>
       </c>
-      <c r="E13" s="14" t="s">
+      <c r="F13" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="F13" s="13" t="s">
+      <c r="G13" s="13" t="s">
         <v>30</v>
-      </c>
-      <c r="G13" s="13" t="s">
-        <v>31</v>
       </c>
       <c r="H13" s="13" t="str">
         <f>CONCATENATE(F13," ",G13)</f>
         <v>{kindNachname} {kindVorname}</v>
       </c>
       <c r="I13" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="J13" s="21" t="s">
         <v>32</v>
       </c>
-      <c r="J13" s="22" t="s">
-        <v>33</v>
-      </c>
-      <c r="K13" s="22" t="str">
+      <c r="K13" s="21" t="str">
         <f>TEXT(J13,"MMM")</f>
         <v>{zeitabschnittVon}</v>
       </c>
@@ -1714,41 +2025,41 @@
         <f>YEAR(J13)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="M13" s="22" t="s">
+      <c r="M13" s="21" t="s">
+        <v>33</v>
+      </c>
+      <c r="N13" s="15" t="s">
         <v>34</v>
       </c>
-      <c r="N13" s="15" t="s">
+      <c r="O13" s="16" t="s">
         <v>35</v>
       </c>
-      <c r="O13" s="16" t="s">
+      <c r="P13" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="P13" s="17" t="s">
+      <c r="Q13" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="Q13" s="17" t="s">
+      <c r="R13" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="R13" s="13" t="s">
+      <c r="S13" s="13" t="s">
         <v>39</v>
-      </c>
-      <c r="S13" s="13" t="s">
-        <v>40</v>
       </c>
       <c r="T13" s="13" t="str">
         <f>IF(A13&lt;&gt;"","x","")</f>
         <v>x</v>
       </c>
       <c r="U13" s="13" t="str">
-        <f>IF(Q13="X","Abrechnung direkt zwischen Gemeinde &amp; Erziehungsberechtigten","Auszahlung an Institution")</f>
+        <f>IF(Q13="X","Abrechnung direkt zwischen Gemeinde &amp; Antragstellenden","Auszahlung an Institution")</f>
         <v>Auszahlung an Institution</v>
       </c>
       <c r="V13" s="13" t="str">
-        <f>IF(Q13="X","Ausserhalb von kiBon","Auszahlung an Institution")</f>
+        <f>IF(Q13="X","Abrechnung direkt zwischen Gemeinde &amp; Antragstellenden","Auszahlung an Institution")</f>
         <v>Auszahlung an Institution</v>
       </c>
       <c r="W13" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
   </sheetData>
@@ -1758,12 +2069,12 @@
     <sortCondition ref="J13"/>
   </sortState>
   <conditionalFormatting sqref="A13:P13 R13:W13">
-    <cfRule type="expression" dxfId="31" priority="4">
+    <cfRule type="expression" dxfId="27" priority="4">
       <formula>$N13="X"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q13">
-    <cfRule type="expression" dxfId="30" priority="1">
+    <cfRule type="expression" dxfId="26" priority="1">
       <formula>$M13="X"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -1777,161 +2088,161 @@
   <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="26.83203125" style="27" customWidth="1"/>
-    <col min="2" max="2" width="22.33203125" style="27" customWidth="1"/>
-    <col min="3" max="3" width="26.83203125" style="27" customWidth="1"/>
-    <col min="4" max="4" width="24.33203125" style="27" customWidth="1"/>
-    <col min="5" max="5" width="13.5" style="27" customWidth="1"/>
-    <col min="6" max="6" width="16.83203125" style="27" customWidth="1"/>
-    <col min="7" max="7" width="13.33203125" style="27" customWidth="1"/>
-    <col min="8" max="8" width="25.6640625" style="27" customWidth="1"/>
-    <col min="9" max="16384" width="11.5" style="27"/>
+    <col min="1" max="1" width="26.83203125" style="26" customWidth="1"/>
+    <col min="2" max="2" width="22.33203125" style="26" customWidth="1"/>
+    <col min="3" max="3" width="26.83203125" style="26" customWidth="1"/>
+    <col min="4" max="4" width="24.33203125" style="26" customWidth="1"/>
+    <col min="5" max="5" width="13.5" style="26" customWidth="1"/>
+    <col min="6" max="6" width="16.83203125" style="26" customWidth="1"/>
+    <col min="7" max="7" width="13.33203125" style="26" customWidth="1"/>
+    <col min="8" max="8" width="25.6640625" style="26" customWidth="1"/>
+    <col min="9" max="16384" width="11.5" style="26"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" customFormat="1" ht="21" x14ac:dyDescent="0.25">
-      <c r="A1" s="29" t="s">
-        <v>49</v>
-      </c>
-      <c r="B1" s="31"/>
-      <c r="C1" s="31"/>
-      <c r="D1" s="31"/>
-      <c r="E1" s="34"/>
+      <c r="A1" s="28" t="s">
+        <v>48</v>
+      </c>
+      <c r="B1" s="30"/>
+      <c r="C1" s="30"/>
+      <c r="D1" s="30"/>
+      <c r="E1" s="33"/>
     </row>
     <row r="2" spans="1:5" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="30" t="s">
+      <c r="A2" s="29" t="s">
+        <v>51</v>
+      </c>
+      <c r="B2" s="30"/>
+      <c r="C2" s="30"/>
+      <c r="D2" s="30"/>
+      <c r="E2" s="33"/>
+    </row>
+    <row r="3" spans="1:5" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="29" t="s">
         <v>53</v>
       </c>
-      <c r="B2" s="31"/>
-      <c r="C2" s="31"/>
-      <c r="D2" s="31"/>
-      <c r="E2" s="34"/>
-    </row>
-    <row r="3" spans="1:5" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="30" t="s">
-        <v>55</v>
-      </c>
-      <c r="B3" s="31"/>
-      <c r="C3" s="31"/>
-      <c r="D3" s="31"/>
-      <c r="E3" s="34"/>
+      <c r="B3" s="30"/>
+      <c r="C3" s="30"/>
+      <c r="D3" s="30"/>
+      <c r="E3" s="33"/>
     </row>
     <row r="4" spans="1:5" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="30" t="s">
-        <v>54</v>
-      </c>
-      <c r="B4" s="31"/>
-      <c r="C4" s="31"/>
-      <c r="D4" s="31"/>
-      <c r="E4" s="34"/>
+      <c r="A4" s="29" t="s">
+        <v>52</v>
+      </c>
+      <c r="B4" s="30"/>
+      <c r="C4" s="30"/>
+      <c r="D4" s="30"/>
+      <c r="E4" s="33"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A5" s="32"/>
-      <c r="B5" s="31"/>
-      <c r="C5" s="31"/>
-      <c r="D5" s="31"/>
-      <c r="E5" s="31"/>
+      <c r="A5" s="31"/>
+      <c r="B5" s="30"/>
+      <c r="C5" s="30"/>
+      <c r="D5" s="30"/>
+      <c r="E5" s="30"/>
     </row>
     <row r="6" spans="1:5" ht="16" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="28" t="s">
-        <v>24</v>
-      </c>
-      <c r="B6" s="27" t="s">
-        <v>43</v>
+      <c r="A6" s="27" t="s">
+        <v>23</v>
+      </c>
+      <c r="B6" s="26" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="16" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="28" t="s">
-        <v>42</v>
-      </c>
-      <c r="B8" s="28" t="s">
-        <v>62</v>
+      <c r="A8" s="27" t="s">
+        <v>41</v>
+      </c>
+      <c r="B8" s="27" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="49.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="28" t="s">
-        <v>47</v>
-      </c>
-      <c r="B9" s="27" t="s">
-        <v>50</v>
-      </c>
-      <c r="C9" s="27" t="s">
+      <c r="A9" s="27" t="s">
         <v>46</v>
       </c>
+      <c r="B9" s="26" t="s">
+        <v>63</v>
+      </c>
+      <c r="C9" s="26" t="s">
+        <v>45</v>
+      </c>
     </row>
     <row r="10" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A10" s="33" t="s">
+      <c r="A10" s="32" t="s">
+        <v>26</v>
+      </c>
+      <c r="B10" s="36">
+        <v>0</v>
+      </c>
+      <c r="C10" s="36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="A11" s="32" t="s">
         <v>27</v>
       </c>
-      <c r="B10" s="37">
-        <v>0</v>
-      </c>
-      <c r="C10" s="37">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A11" s="33" t="s">
-        <v>28</v>
-      </c>
-      <c r="B11" s="37">
-        <v>0</v>
-      </c>
-      <c r="C11" s="37">
+      <c r="B11" s="36">
+        <v>0</v>
+      </c>
+      <c r="C11" s="36">
         <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="32" x14ac:dyDescent="0.2">
-      <c r="A12" s="33" t="s">
+      <c r="A12" s="32" t="s">
+        <v>44</v>
+      </c>
+      <c r="B12" s="36">
+        <v>0</v>
+      </c>
+      <c r="C12" s="36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="A13" s="32" t="s">
+        <v>31</v>
+      </c>
+      <c r="B13" s="36">
+        <v>0</v>
+      </c>
+      <c r="C13" s="36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="A14" s="32" t="s">
+        <v>61</v>
+      </c>
+      <c r="B14" s="36">
+        <v>0</v>
+      </c>
+      <c r="C14" s="36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="A15" s="32" t="s">
+        <v>32</v>
+      </c>
+      <c r="B15" s="36">
+        <v>0</v>
+      </c>
+      <c r="C15" s="36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="A16" s="32" t="s">
         <v>45</v>
       </c>
-      <c r="B12" s="37">
-        <v>0</v>
-      </c>
-      <c r="C12" s="37">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A13" s="33" t="s">
-        <v>32</v>
-      </c>
-      <c r="B13" s="37">
-        <v>0</v>
-      </c>
-      <c r="C13" s="37">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A14" s="33" t="s">
-        <v>63</v>
-      </c>
-      <c r="B14" s="37">
-        <v>0</v>
-      </c>
-      <c r="C14" s="37">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A15" s="33" t="s">
-        <v>33</v>
-      </c>
-      <c r="B15" s="37">
-        <v>0</v>
-      </c>
-      <c r="C15" s="37">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A16" s="33" t="s">
-        <v>46</v>
-      </c>
-      <c r="B16" s="37">
-        <v>0</v>
-      </c>
-      <c r="C16" s="37">
+      <c r="B16" s="36">
+        <v>0</v>
+      </c>
+      <c r="C16" s="36">
         <v>0</v>
       </c>
     </row>
@@ -1946,8 +2257,8 @@
   <dimension ref="A1:D15"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="21" customWidth="1"/>
-    <col min="2" max="4" width="22.83203125" style="27" customWidth="1"/>
+    <col min="1" max="1" width="22.5" customWidth="1"/>
+    <col min="2" max="4" width="22.83203125" style="26" customWidth="1"/>
     <col min="5" max="5" width="13.5" customWidth="1"/>
     <col min="6" max="6" width="16.83203125" customWidth="1"/>
     <col min="7" max="7" width="13.33203125" customWidth="1"/>
@@ -1955,121 +2266,121 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="21" x14ac:dyDescent="0.25">
-      <c r="A1" s="29" t="s">
-        <v>48</v>
-      </c>
-      <c r="B1" s="35"/>
-      <c r="C1" s="35"/>
-      <c r="D1" s="35"/>
+      <c r="A1" s="28" t="s">
+        <v>47</v>
+      </c>
+      <c r="B1" s="34"/>
+      <c r="C1" s="34"/>
+      <c r="D1" s="34"/>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A2" s="30" t="s">
+      <c r="A2" s="29" t="s">
+        <v>51</v>
+      </c>
+      <c r="B2" s="34"/>
+      <c r="C2" s="34"/>
+      <c r="D2" s="34"/>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A3" s="29" t="s">
         <v>53</v>
       </c>
-      <c r="B2" s="35"/>
-      <c r="C2" s="35"/>
-      <c r="D2" s="35"/>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A3" s="30" t="s">
-        <v>55</v>
-      </c>
-      <c r="B3" s="35"/>
-      <c r="C3" s="35"/>
-      <c r="D3" s="35"/>
+      <c r="B3" s="34"/>
+      <c r="C3" s="34"/>
+      <c r="D3" s="34"/>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A4" s="30" t="s">
-        <v>54</v>
-      </c>
-      <c r="B4" s="35"/>
-      <c r="C4" s="35"/>
-      <c r="D4" s="35"/>
+      <c r="A4" s="29" t="s">
+        <v>52</v>
+      </c>
+      <c r="B4" s="34"/>
+      <c r="C4" s="34"/>
+      <c r="D4" s="34"/>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A5" s="6"/>
     </row>
     <row r="6" spans="1:4" hidden="1" x14ac:dyDescent="0.2"/>
     <row r="7" spans="1:4" ht="16" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="24" t="s">
-        <v>24</v>
-      </c>
-      <c r="B7" s="27" t="s">
-        <v>64</v>
+      <c r="A7" s="23" t="s">
+        <v>23</v>
+      </c>
+      <c r="B7" s="26" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="8" spans="1:4" hidden="1" x14ac:dyDescent="0.2"/>
     <row r="9" spans="1:4" ht="16" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="24" t="s">
-        <v>42</v>
-      </c>
-      <c r="B9" s="28" t="s">
-        <v>62</v>
+      <c r="A9" s="23" t="s">
+        <v>41</v>
+      </c>
+      <c r="B9" s="27" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="51.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="24" t="s">
-        <v>47</v>
-      </c>
-      <c r="B10" s="27" t="s">
-        <v>50</v>
-      </c>
-      <c r="C10" s="27" t="s">
+      <c r="A10" s="23" t="s">
         <v>46</v>
+      </c>
+      <c r="B10" s="26" t="s">
+        <v>63</v>
+      </c>
+      <c r="C10" s="26" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A11" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="B11" s="36">
+        <v>0</v>
+      </c>
+      <c r="C11" s="36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A12" s="24" t="s">
         <v>27</v>
       </c>
-      <c r="B11" s="37">
-        <v>0</v>
-      </c>
-      <c r="C11" s="37">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A12" s="25" t="s">
-        <v>28</v>
-      </c>
-      <c r="B12" s="37">
-        <v>0</v>
-      </c>
-      <c r="C12" s="37">
+      <c r="B12" s="36">
+        <v>0</v>
+      </c>
+      <c r="C12" s="36">
         <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A13" s="26" t="s">
-        <v>63</v>
-      </c>
-      <c r="B13" s="37">
-        <v>0</v>
-      </c>
-      <c r="C13" s="37">
+      <c r="A13" s="25" t="s">
+        <v>61</v>
+      </c>
+      <c r="B13" s="36">
+        <v>0</v>
+      </c>
+      <c r="C13" s="36">
         <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A14" s="36" t="s">
-        <v>33</v>
-      </c>
-      <c r="B14" s="37">
-        <v>0</v>
-      </c>
-      <c r="C14" s="37">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A15" s="12" t="s">
-        <v>46</v>
-      </c>
-      <c r="B15" s="37">
-        <v>0</v>
-      </c>
-      <c r="C15" s="37">
+      <c r="A14" s="35" t="s">
+        <v>32</v>
+      </c>
+      <c r="B14" s="36">
+        <v>0</v>
+      </c>
+      <c r="C14" s="36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" ht="32" x14ac:dyDescent="0.2">
+      <c r="A15" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="B15" s="36">
+        <v>0</v>
+      </c>
+      <c r="C15" s="36">
         <v>0</v>
       </c>
     </row>
